--- a/AENA DCF VALUATION.xlsx
+++ b/AENA DCF VALUATION.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniomaria/Desktop/Finance &amp; Career /AENA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA73BFF9-9465-B647-9825-B68808DF613D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F675D317-D9D7-DF40-9162-61FEB0950212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="780" windowWidth="28440" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="920" yWindow="760" windowWidth="28440" windowHeight="18360" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
   <si>
     <t>AENA</t>
   </si>
@@ -374,20 +374,25 @@
   </si>
   <si>
     <t>Forecasts, CoC, Multiples, Valuation &amp; Sensitivity</t>
+  </si>
+  <si>
+    <t>(EUR, fiscal year ending December 31)</t>
+  </si>
+  <si>
+    <t>(fiscal year ending December 31)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;\(#,##0.00\)"/>
     <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="185" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;???_-;_-@_-"/>
   </numFmts>
   <fonts count="31">
@@ -804,7 +809,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="6" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2501,7 +2506,7 @@
     </row>
     <row r="3" spans="1:17" ht="16">
       <c r="A3" s="41" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -3165,7 +3170,7 @@
     </row>
     <row r="3" spans="1:14" ht="16">
       <c r="A3" s="41" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -3346,7 +3351,7 @@
     </row>
     <row r="3" spans="1:15" ht="16">
       <c r="A3" s="41" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -3503,7 +3508,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="86">
-        <f xml:space="preserve"> 1 /(1 + $E$12)</f>
+        <f>1/(1+E12)</f>
         <v>0.93004867373236977</v>
       </c>
       <c r="F14" s="86">
@@ -3547,7 +3552,7 @@
         <v>1972671093.2392576</v>
       </c>
       <c r="G16" s="86">
-        <f t="shared" si="0"/>
+        <f>G14*G10</f>
         <v>1841202413.5400605</v>
       </c>
       <c r="H16" s="86">
@@ -4144,11 +4149,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.1640625" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26">
@@ -4193,7 +4205,7 @@
     </row>
     <row r="3" spans="1:16" ht="16">
       <c r="A3" s="41" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -4238,13 +4250,13 @@
         <v>0.06</v>
       </c>
       <c r="D8" s="84">
-        <v>29.691463115311951</v>
+        <v>30.184208510389791</v>
       </c>
       <c r="E8" s="84">
-        <v>31.236860356057765</v>
+        <v>31.816613395791673</v>
       </c>
       <c r="F8" s="84">
-        <v>32.975432251896791</v>
+        <v>33.653068891868791</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -4252,27 +4264,32 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="D9" s="84">
-        <v>26.564708212004458</v>
+        <v>26.883097803525107</v>
       </c>
       <c r="E9" s="84">
-        <v>27.785953756599987</v>
+        <v>28.173100878922686</v>
       </c>
       <c r="F9" s="84">
-        <v>29.142893250595016</v>
-      </c>
+        <v>29.606437629364436</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
     </row>
     <row r="10" spans="1:16">
       <c r="C10" s="33">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D10" s="84">
-        <v>24.006161256253073</v>
+        <v>24.18216077625198</v>
       </c>
       <c r="E10" s="84">
-        <v>24.992004657285211</v>
+        <v>25.223508296265294</v>
       </c>
       <c r="F10" s="84">
-        <v>26.076432398420554</v>
+        <v>26.368990568279937</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -4280,13 +4297,13 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D11" s="84">
-        <v>21.873776719221699</v>
+        <v>21.931355091807173</v>
       </c>
       <c r="E11" s="84">
-        <v>22.683640702662291</v>
+        <v>22.786815350323913</v>
       </c>
       <c r="F11" s="84">
-        <v>23.567128684597495</v>
+        <v>23.720044723251259</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -4294,30 +4311,61 @@
         <v>0.08</v>
       </c>
       <c r="D12" s="84">
-        <v>20.069215214197847</v>
+        <v>20.026805248137808</v>
       </c>
       <c r="E12" s="84">
-        <v>20.744328479368992</v>
+        <v>20.739928167739464</v>
       </c>
       <c r="F12" s="84">
-        <v>21.475701183304398</v>
-      </c>
+        <v>21.512477997307922</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
     </row>
     <row r="13" spans="1:16">
       <c r="C13" s="33">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="D13" s="84">
-        <v>18.52223416565791</v>
+        <v>18.394314424079131</v>
       </c>
       <c r="E13" s="84">
-        <v>19.092062803539996</v>
+        <v>18.996225070607601</v>
       </c>
       <c r="F13" s="84">
-        <v>19.705724413566859</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" ht="16">
+        <v>19.644436536099796</v>
+      </c>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+    </row>
+    <row r="17" spans="3:13" ht="16">
       <c r="C17" s="80" t="s">
         <v>99</v>
       </c>
@@ -4330,8 +4378,13 @@
       <c r="F17" s="50" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="18" spans="3:6">
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="15"/>
+    </row>
+    <row r="18" spans="3:13">
       <c r="C18" t="s">
         <v>100</v>
       </c>
@@ -4345,8 +4398,13 @@
       <c r="F18" s="12">
         <v>3.3000000000000002E-2</v>
       </c>
-    </row>
-    <row r="19" spans="3:6">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="15"/>
+    </row>
+    <row r="19" spans="3:13">
       <c r="C19" t="s">
         <v>101</v>
       </c>
@@ -4360,8 +4418,13 @@
       <c r="F19" s="79">
         <v>2.8000000000000001E-2</v>
       </c>
-    </row>
-    <row r="20" spans="3:6">
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="15"/>
+    </row>
+    <row r="20" spans="3:13">
       <c r="C20" t="s">
         <v>102</v>
       </c>
@@ -4374,6 +4437,49 @@
       <c r="F20">
         <v>10</v>
       </c>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="15"/>
+    </row>
+    <row r="21" spans="3:13">
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" spans="3:13">
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="3:13">
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+    </row>
+    <row r="24" spans="3:13">
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+    </row>
+    <row r="25" spans="3:13">
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+    </row>
+    <row r="28" spans="3:13">
+      <c r="F28" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/AENA DCF VALUATION.xlsx
+++ b/AENA DCF VALUATION.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniomaria/Desktop/Finance &amp; Career /AENA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F675D317-D9D7-DF40-9162-61FEB0950212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E084EDF7-285D-D443-B388-76A507E73461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="760" windowWidth="28440" windowHeight="18360" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="920" yWindow="760" windowWidth="28440" windowHeight="18360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="5" r:id="rId1"/>
@@ -672,7 +672,7 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="4" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="4"/>
@@ -682,7 +682,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -824,12 +823,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="185" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="_x000a_386grabber=M" xfId="6" xr:uid="{B52C3E28-7C4F-4347-98B2-3507D3681DDE}"/>
@@ -1143,36 +1146,36 @@
   <dimension ref="C6:O21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="16384" width="9.1640625" style="26"/>
+    <col min="1" max="16384" width="9.1640625" style="25"/>
   </cols>
   <sheetData>
     <row r="6" spans="7:15" ht="59">
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="28"/>
-      <c r="O6" s="28"/>
+      <c r="H6" s="27"/>
+      <c r="O6" s="27"/>
     </row>
     <row r="7" spans="7:15" ht="34">
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="28" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="8" spans="7:15" ht="34">
-      <c r="G8" s="30"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="12" spans="7:15" ht="30">
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="30" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="3:3" ht="24">
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="31" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="3:3" ht="24">
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="31" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1234,7 +1237,7 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16" ht="16">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="40" t="s">
         <v>94</v>
       </c>
       <c r="B3" s="1"/>
@@ -1249,828 +1252,828 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="40"/>
+      <c r="N3" s="39"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="40"/>
+      <c r="P3" s="39"/>
     </row>
     <row r="5" spans="1:16" ht="16">
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="51" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
     </row>
     <row r="6" spans="1:16" ht="16">
-      <c r="C6" s="44">
+      <c r="C6" s="43">
         <v>2020</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="43">
         <v>2021</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="43">
         <v>2022</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="43">
         <v>2023</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="43">
         <v>2024</v>
       </c>
-      <c r="H6" s="44">
+      <c r="H6" s="43">
         <v>2025</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="44">
         <v>2026</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="44">
         <v>2027</v>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="44">
         <v>2028</v>
       </c>
-      <c r="L6" s="45">
+      <c r="L6" s="44">
         <v>2029</v>
       </c>
-      <c r="M6" s="45">
+      <c r="M6" s="44">
         <v>2030</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="16">
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
     </row>
     <row r="8" spans="1:16" ht="16">
       <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>2042183</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>2134973</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>3667058</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>4386767</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>5021501</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <v>5357335</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="33">
         <v>5622758.8052399997</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="33">
         <v>5867022.6932572369</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="33">
         <v>6098030.8447815478</v>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="33">
         <v>6325731.3165256903</v>
       </c>
-      <c r="M8" s="34">
+      <c r="M8" s="33">
         <f>L8*(1+(SUM(M33:M36)/4))</f>
         <v>6502345.7348830868</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="16">
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="59">
+      <c r="C9" s="52"/>
+      <c r="D9" s="58">
         <f>(D8-C8)/C8</f>
         <v>4.5436672423578101E-2</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="58">
         <f t="shared" ref="E9:M9" si="0">(E8-D8)/D8</f>
         <v>0.71761329065988189</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="58">
         <f t="shared" si="0"/>
         <v>0.19626332607774408</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="58">
         <f t="shared" si="0"/>
         <v>0.14469289114283937</v>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="58">
         <f t="shared" si="0"/>
         <v>6.6879206038194555E-2</v>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="59">
         <f t="shared" si="0"/>
         <v>4.9543999999999935E-2</v>
       </c>
-      <c r="J9" s="60">
+      <c r="J9" s="59">
         <f t="shared" si="0"/>
         <v>4.3442000000000203E-2</v>
       </c>
-      <c r="K9" s="60">
+      <c r="K9" s="59">
         <f t="shared" si="0"/>
         <v>3.9374000000000083E-2</v>
       </c>
-      <c r="L9" s="60">
+      <c r="L9" s="59">
         <f t="shared" si="0"/>
         <v>3.7339999999999915E-2</v>
       </c>
-      <c r="M9" s="60">
+      <c r="M9" s="59">
         <f t="shared" si="0"/>
         <v>2.7919999999999879E-2</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="16">
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="52">
         <f>C14+C12</f>
         <v>815081</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="52">
         <f>D14+D12</f>
         <v>707494</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="52">
         <f t="shared" ref="E10:M10" si="1">E14+E12</f>
         <v>1892306</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="52">
         <f t="shared" si="1"/>
         <v>2676426</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="52">
         <f t="shared" si="1"/>
         <v>3182790</v>
       </c>
-      <c r="H10" s="53">
+      <c r="H10" s="52">
         <f t="shared" si="1"/>
         <v>3401061</v>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="53">
         <f t="shared" si="1"/>
         <v>3742928.9758388959</v>
       </c>
-      <c r="J10" s="54">
+      <c r="J10" s="53">
         <f t="shared" si="1"/>
         <v>3805541.4219971406</v>
       </c>
-      <c r="K10" s="54">
+      <c r="K10" s="53">
         <f t="shared" si="1"/>
         <v>3922614.7309006643</v>
       </c>
-      <c r="L10" s="54">
+      <c r="L10" s="53">
         <f t="shared" si="1"/>
         <v>4001165.364545933</v>
       </c>
-      <c r="M10" s="54">
+      <c r="M10" s="53">
         <f t="shared" si="1"/>
         <v>4044459.0470972797</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16">
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="58">
         <f>C10/C8</f>
         <v>0.39912240969589896</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="58">
         <f t="shared" ref="D11:M11" si="2">D10/D8</f>
         <v>0.33138311351010058</v>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="58">
         <f t="shared" si="2"/>
         <v>0.51602838024378128</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="58">
         <f t="shared" si="2"/>
         <v>0.61011355287390467</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="58">
         <f t="shared" si="2"/>
         <v>0.63383239393958102</v>
       </c>
-      <c r="H11" s="59">
+      <c r="H11" s="58">
         <f t="shared" si="2"/>
         <v>0.63484195033538127</v>
       </c>
-      <c r="I11" s="60">
+      <c r="I11" s="59">
         <f t="shared" si="2"/>
         <v>0.66567482360274111</v>
       </c>
-      <c r="J11" s="60">
+      <c r="J11" s="59">
         <f t="shared" si="2"/>
         <v>0.6486324701574302</v>
       </c>
-      <c r="K11" s="60">
+      <c r="K11" s="59">
         <f t="shared" si="2"/>
         <v>0.64325924724658978</v>
       </c>
-      <c r="L11" s="60">
+      <c r="L11" s="59">
         <f t="shared" si="2"/>
         <v>0.63252218033558705</v>
       </c>
-      <c r="M11" s="60">
+      <c r="M11" s="59">
         <f t="shared" si="2"/>
         <v>0.622</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="16">
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="53">
+      <c r="C12" s="52">
         <v>721370</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="52">
         <v>715550</v>
       </c>
-      <c r="E12" s="53">
+      <c r="E12" s="52">
         <v>718685</v>
       </c>
-      <c r="F12" s="53">
+      <c r="F12" s="52">
         <v>731721</v>
       </c>
-      <c r="G12" s="53">
+      <c r="G12" s="52">
         <v>730480</v>
       </c>
-      <c r="H12" s="53">
+      <c r="H12" s="52">
         <v>668339</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="33">
         <v>819094.39711409539</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="33">
         <v>813359.84843595012</v>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="33">
         <v>873599.30850989057</v>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="33">
         <v>901557.01944834448</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="33">
         <f>M8*M28</f>
         <v>923333.09435339819</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="16">
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="58">
         <f>C12/C8</f>
         <v>0.35323474928544601</v>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="58">
         <f t="shared" ref="D13:M13" si="3">D12/D8</f>
         <v>0.33515646333700705</v>
       </c>
-      <c r="E13" s="59">
+      <c r="E13" s="58">
         <f t="shared" si="3"/>
         <v>0.19598408315330709</v>
       </c>
-      <c r="F13" s="59">
+      <c r="F13" s="58">
         <f t="shared" si="3"/>
         <v>0.16680188393867282</v>
       </c>
-      <c r="G13" s="59">
+      <c r="G13" s="58">
         <f t="shared" si="3"/>
         <v>0.14547044797959813</v>
       </c>
-      <c r="H13" s="59">
+      <c r="H13" s="58">
         <f t="shared" si="3"/>
         <v>0.12475213888995182</v>
       </c>
-      <c r="I13" s="60">
+      <c r="I13" s="59">
         <f t="shared" si="3"/>
         <v>0.14567482360274095</v>
       </c>
-      <c r="J13" s="60">
+      <c r="J13" s="59">
         <f t="shared" si="3"/>
         <v>0.13863247015743027</v>
       </c>
-      <c r="K13" s="60">
+      <c r="K13" s="59">
         <f t="shared" si="3"/>
         <v>0.14325924724658978</v>
       </c>
-      <c r="L13" s="60">
+      <c r="L13" s="59">
         <f t="shared" si="3"/>
         <v>0.14252218033558697</v>
       </c>
-      <c r="M13" s="60">
+      <c r="M13" s="59">
         <f t="shared" si="3"/>
         <v>0.14199999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="16">
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="53">
+      <c r="C14" s="52">
         <v>93711</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="52">
         <v>-8056</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="52">
         <v>1173621</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="52">
         <v>1944705</v>
       </c>
-      <c r="G14" s="53">
+      <c r="G14" s="52">
         <v>2452310</v>
       </c>
-      <c r="H14" s="53">
+      <c r="H14" s="52">
         <v>2732722</v>
       </c>
-      <c r="I14" s="54">
+      <c r="I14" s="53">
         <v>2923834.5787248006</v>
       </c>
-      <c r="J14" s="54">
+      <c r="J14" s="53">
         <v>2992181.5735611906</v>
       </c>
-      <c r="K14" s="54">
+      <c r="K14" s="53">
         <v>3049015.4223907739</v>
       </c>
-      <c r="L14" s="54">
+      <c r="L14" s="53">
         <f>L27*L8</f>
         <v>3099608.3450975884</v>
       </c>
-      <c r="M14" s="54">
+      <c r="M14" s="53">
         <f>M8*M27</f>
         <v>3121125.9527438814</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16">
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="59">
+      <c r="C15" s="58">
         <f>C14/C8</f>
         <v>4.5887660410452932E-2</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="58">
         <f t="shared" ref="D15:M15" si="4">D14/D8</f>
         <v>-3.7733498269064761E-3</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="58">
         <f t="shared" si="4"/>
         <v>0.32004429709047416</v>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="58">
         <f t="shared" si="4"/>
         <v>0.44331166893523177</v>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="58">
         <f t="shared" si="4"/>
         <v>0.48836194595998289</v>
       </c>
-      <c r="H15" s="59">
+      <c r="H15" s="58">
         <f t="shared" si="4"/>
         <v>0.51008981144542953</v>
       </c>
-      <c r="I15" s="60">
+      <c r="I15" s="59">
         <f t="shared" si="4"/>
         <v>0.52000000000000013</v>
       </c>
-      <c r="J15" s="60">
+      <c r="J15" s="59">
         <f t="shared" si="4"/>
         <v>0.51</v>
       </c>
-      <c r="K15" s="60">
+      <c r="K15" s="59">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="L15" s="60">
+      <c r="L15" s="59">
         <f t="shared" si="4"/>
         <v>0.49000000000000005</v>
       </c>
-      <c r="M15" s="60">
+      <c r="M15" s="59">
         <f t="shared" si="4"/>
         <v>0.48</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16">
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="53">
+      <c r="C16" s="52">
         <v>70283.25</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="52">
         <v>-6042</v>
       </c>
-      <c r="E16" s="53">
+      <c r="E16" s="52">
         <v>880215.75</v>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="52">
         <v>1458528.75</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="52">
         <v>1839232.5</v>
       </c>
-      <c r="H16" s="53">
+      <c r="H16" s="52">
         <v>2049541.5</v>
       </c>
-      <c r="I16" s="54">
+      <c r="I16" s="53">
         <v>2192875.9340436002</v>
       </c>
-      <c r="J16" s="54">
+      <c r="J16" s="53">
         <v>2244136.1801708927</v>
       </c>
-      <c r="K16" s="54">
+      <c r="K16" s="53">
         <v>2286761.5667930804</v>
       </c>
-      <c r="L16" s="54">
+      <c r="L16" s="53">
         <v>2324706.2588231913</v>
       </c>
-      <c r="M16" s="54">
+      <c r="M16" s="53">
         <f>M14*(1-0.25)</f>
         <v>2340844.4645579113</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="16">
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="62">
+      <c r="C17" s="61">
         <f>C16/C8</f>
         <v>3.4415745307839696E-2</v>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="61">
         <f t="shared" ref="D17:M17" si="5">D16/D8</f>
         <v>-2.8300123701798571E-3</v>
       </c>
-      <c r="E17" s="62">
+      <c r="E17" s="61">
         <f t="shared" si="5"/>
         <v>0.24003322281785563</v>
       </c>
-      <c r="F17" s="62">
+      <c r="F17" s="61">
         <f t="shared" si="5"/>
         <v>0.33248375170142386</v>
       </c>
-      <c r="G17" s="62">
+      <c r="G17" s="61">
         <f t="shared" si="5"/>
         <v>0.36627145946998718</v>
       </c>
-      <c r="H17" s="62">
+      <c r="H17" s="61">
         <f t="shared" si="5"/>
         <v>0.38256735858407209</v>
       </c>
-      <c r="I17" s="63">
+      <c r="I17" s="62">
         <f t="shared" si="5"/>
         <v>0.39000000000000007</v>
       </c>
-      <c r="J17" s="63">
+      <c r="J17" s="62">
         <f t="shared" si="5"/>
         <v>0.38249999999999995</v>
       </c>
-      <c r="K17" s="63">
+      <c r="K17" s="62">
         <f t="shared" si="5"/>
         <v>0.375</v>
       </c>
-      <c r="L17" s="63">
+      <c r="L17" s="62">
         <f t="shared" si="5"/>
         <v>0.36749999999999999</v>
       </c>
-      <c r="M17" s="63">
+      <c r="M17" s="62">
         <f t="shared" si="5"/>
         <v>0.36</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="16">
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="53">
+      <c r="C18" s="52">
         <v>489753</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="52">
         <v>652004</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="52">
         <v>555419</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="52">
         <v>552067</v>
       </c>
-      <c r="G18" s="53">
+      <c r="G18" s="52">
         <v>742953</v>
       </c>
-      <c r="H18" s="53">
+      <c r="H18" s="52">
         <v>690024</v>
       </c>
-      <c r="I18" s="54">
+      <c r="I18" s="53">
         <v>753340.48625817301</v>
       </c>
-      <c r="J18" s="54">
+      <c r="J18" s="53">
         <v>801971.26975479082</v>
       </c>
-      <c r="K18" s="54">
+      <c r="K18" s="53">
         <v>829506.65099844593</v>
       </c>
-      <c r="L18" s="54">
+      <c r="L18" s="53">
         <v>857559.45083789132</v>
       </c>
-      <c r="M18" s="54">
+      <c r="M18" s="53">
         <f>M29*M8</f>
         <v>890821.36567898293</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="16">
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="59">
+      <c r="C19" s="58">
         <f>C18/C8</f>
         <v>0.2398183708316052</v>
       </c>
-      <c r="D19" s="59">
+      <c r="D19" s="58">
         <f t="shared" ref="D19:M19" si="6">D18/D8</f>
         <v>0.30539215250028923</v>
       </c>
-      <c r="E19" s="59">
+      <c r="E19" s="58">
         <f t="shared" si="6"/>
         <v>0.15146174399205031</v>
       </c>
-      <c r="F19" s="59">
+      <c r="F19" s="58">
         <f t="shared" si="6"/>
         <v>0.12584826137335309</v>
       </c>
-      <c r="G19" s="59">
+      <c r="G19" s="58">
         <f t="shared" si="6"/>
         <v>0.14795436663260647</v>
       </c>
-      <c r="H19" s="59">
+      <c r="H19" s="58">
         <f t="shared" si="6"/>
         <v>0.1287998603783411</v>
       </c>
-      <c r="I19" s="60">
+      <c r="I19" s="59">
         <f t="shared" si="6"/>
         <v>0.13398058005904767</v>
       </c>
-      <c r="J19" s="60">
+      <c r="J19" s="59">
         <f t="shared" si="6"/>
         <v>0.13669135295427923</v>
       </c>
-      <c r="K19" s="60">
+      <c r="K19" s="59">
         <f t="shared" si="6"/>
         <v>0.13602860859720065</v>
       </c>
-      <c r="L19" s="60">
+      <c r="L19" s="59">
         <f t="shared" si="6"/>
         <v>0.1355668472035092</v>
       </c>
-      <c r="M19" s="60">
+      <c r="M19" s="59">
         <f t="shared" si="6"/>
         <v>0.13700000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="16">
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="55" t="s">
+      <c r="C20" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="52">
         <v>-228789</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="52">
         <v>-51213</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="52">
         <v>191167</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="52">
         <v>-126574</v>
       </c>
-      <c r="H20" s="53">
+      <c r="H20" s="52">
         <v>59877</v>
       </c>
-      <c r="I20" s="54">
+      <c r="I20" s="53">
         <v>68716.146779303148</v>
       </c>
-      <c r="J20" s="54">
+      <c r="J20" s="53">
         <v>-25044.810701805633</v>
       </c>
-      <c r="K20" s="54">
+      <c r="K20" s="53">
         <v>42177.240264970576</v>
       </c>
-      <c r="L20" s="54">
+      <c r="L20" s="53">
         <v>17922.480409075855</v>
       </c>
-      <c r="M20" s="54">
+      <c r="M20" s="53">
         <v>9962.700043230725</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="16">
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="61">
+      <c r="C21" s="55"/>
+      <c r="D21" s="60">
         <f>D20/D8</f>
         <v>-0.1071624793381462</v>
       </c>
-      <c r="E21" s="61">
+      <c r="E21" s="60">
         <f t="shared" ref="E21:M21" si="7">E20/E8</f>
         <v>-1.3965691298037828E-2</v>
       </c>
-      <c r="F21" s="61">
+      <c r="F21" s="60">
         <f t="shared" si="7"/>
         <v>4.3578106610175554E-2</v>
       </c>
-      <c r="G21" s="61">
+      <c r="G21" s="60">
         <f t="shared" si="7"/>
         <v>-2.5206407406868983E-2</v>
       </c>
-      <c r="H21" s="61">
+      <c r="H21" s="60">
         <f t="shared" si="7"/>
         <v>1.1176639131209828E-2</v>
       </c>
-      <c r="I21" s="60">
+      <c r="I21" s="59">
         <f t="shared" si="7"/>
         <v>1.2221073170569708E-2</v>
       </c>
-      <c r="J21" s="60">
+      <c r="J21" s="59">
         <f t="shared" si="7"/>
         <v>-4.268742769750789E-3</v>
       </c>
-      <c r="K21" s="60">
+      <c r="K21" s="59">
         <f t="shared" si="7"/>
         <v>6.916534425381626E-3</v>
       </c>
-      <c r="L21" s="60">
+      <c r="L21" s="59">
         <f t="shared" si="7"/>
         <v>2.8332661493627111E-3</v>
       </c>
-      <c r="M21" s="60">
+      <c r="M21" s="59">
         <f t="shared" si="7"/>
         <v>1.5321701505018259E-3</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="16">
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="20">
         <v>286293</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="20">
         <v>1094694.75</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="20">
         <v>1447015.75</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="20">
         <v>1953333.5</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="20">
         <v>1967979.5</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="42">
         <v>2189913.6981202201</v>
       </c>
-      <c r="J22" s="43">
+      <c r="J22" s="42">
         <v>2280569.5695538577</v>
       </c>
-      <c r="K22" s="43">
+      <c r="K22" s="42">
         <v>2288676.9840395544</v>
       </c>
-      <c r="L22" s="43">
+      <c r="L22" s="42">
         <v>2350781.3470245688</v>
       </c>
-      <c r="M22" s="43">
+      <c r="M22" s="42">
         <f>M16+M12-M18-M20</f>
         <v>2363393.493189096</v>
       </c>
     </row>
     <row r="23" spans="2:13">
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="52"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="52"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="51"/>
     </row>
     <row r="24" spans="2:13">
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="52"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
     </row>
     <row r="25" spans="2:13" ht="16">
-      <c r="B25" s="22"/>
-      <c r="C25" s="44">
+      <c r="B25" s="21"/>
+      <c r="C25" s="43">
         <v>2020</v>
       </c>
-      <c r="D25" s="44">
+      <c r="D25" s="43">
         <v>2021</v>
       </c>
-      <c r="E25" s="44">
+      <c r="E25" s="43">
         <v>2022</v>
       </c>
-      <c r="F25" s="44">
+      <c r="F25" s="43">
         <v>2023</v>
       </c>
-      <c r="G25" s="44">
+      <c r="G25" s="43">
         <v>2024</v>
       </c>
-      <c r="H25" s="44">
+      <c r="H25" s="43">
         <v>2025</v>
       </c>
-      <c r="I25" s="45">
+      <c r="I25" s="44">
         <v>2026</v>
       </c>
-      <c r="J25" s="45">
+      <c r="J25" s="44">
         <v>2027</v>
       </c>
-      <c r="K25" s="45">
+      <c r="K25" s="44">
         <v>2028</v>
       </c>
-      <c r="L25" s="45">
+      <c r="L25" s="44">
         <v>2029</v>
       </c>
-      <c r="M25" s="45">
+      <c r="M25" s="44">
         <v>2030</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="16">
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="36"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37"/>
     </row>
     <row r="27" spans="2:13" ht="16">
       <c r="B27" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="46">
+      <c r="C27" s="45">
         <v>4.5887660410452932E-2</v>
       </c>
-      <c r="D27" s="46">
+      <c r="D27" s="45">
         <v>-3.7733498269064761E-3</v>
       </c>
-      <c r="E27" s="46">
+      <c r="E27" s="45">
         <v>0.32004429709047416</v>
       </c>
-      <c r="F27" s="46">
+      <c r="F27" s="45">
         <v>0.44331166893523177</v>
       </c>
-      <c r="G27" s="46">
+      <c r="G27" s="45">
         <f>G14/G8</f>
         <v>0.48836194595998289</v>
       </c>
@@ -2078,19 +2081,19 @@
         <f>H14/H8</f>
         <v>0.51008981144542953</v>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="34">
         <v>0.52</v>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="34">
         <v>0.51</v>
       </c>
-      <c r="K27" s="35">
+      <c r="K27" s="34">
         <v>0.5</v>
       </c>
-      <c r="L27" s="35">
+      <c r="L27" s="34">
         <v>0.49</v>
       </c>
-      <c r="M27" s="35">
+      <c r="M27" s="34">
         <v>0.48</v>
       </c>
     </row>
@@ -2098,37 +2101,37 @@
       <c r="B28" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="16">
         <v>0.35323474928544601</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="16">
         <v>0.33515646333700705</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="16">
         <v>0.19598408315330709</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="16">
         <v>0.16680188393867282</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="16">
         <v>0.12475213888995182</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="16">
         <v>0.14547044797959813</v>
       </c>
-      <c r="I28" s="35">
+      <c r="I28" s="34">
         <v>0.14567482360274092</v>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="34">
         <v>0.13863247015743027</v>
       </c>
-      <c r="K28" s="35">
+      <c r="K28" s="34">
         <v>0.14325924724658978</v>
       </c>
-      <c r="L28" s="35">
+      <c r="L28" s="34">
         <v>0.14252218033558697</v>
       </c>
-      <c r="M28" s="35">
+      <c r="M28" s="34">
         <v>0.14199999999999999</v>
       </c>
     </row>
@@ -2136,37 +2139,37 @@
       <c r="B29" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="16">
         <v>0.23981837083160498</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="16">
         <v>0.305392152500289</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="16">
         <v>0.15146174399205001</v>
       </c>
-      <c r="F29" s="47">
+      <c r="F29" s="46">
         <v>0.125848261373353</v>
       </c>
-      <c r="G29" s="47">
+      <c r="G29" s="46">
         <v>0.138679586025515</v>
       </c>
-      <c r="H29" s="47">
+      <c r="H29" s="46">
         <v>0.13741389277827501</v>
       </c>
-      <c r="I29" s="35">
+      <c r="I29" s="34">
         <v>0.13398058005904767</v>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="34">
         <v>0.13669135295427923</v>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="34">
         <v>0.13602860859720065</v>
       </c>
-      <c r="L29" s="35">
+      <c r="L29" s="34">
         <v>0.1355668472035092</v>
       </c>
-      <c r="M29" s="35">
+      <c r="M29" s="34">
         <v>0.13700000000000001</v>
       </c>
     </row>
@@ -2174,37 +2177,37 @@
       <c r="B30" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="16">
         <v>0.27538178507998551</v>
       </c>
-      <c r="D30" s="46">
+      <c r="D30" s="45">
         <v>0.15625068794781011</v>
       </c>
-      <c r="E30" s="46">
+      <c r="E30" s="45">
         <v>7.7003963395179453E-2</v>
       </c>
-      <c r="F30" s="46">
+      <c r="F30" s="45">
         <v>0.10794851880667471</v>
       </c>
-      <c r="G30" s="46">
+      <c r="G30" s="45">
         <v>6.4765597073918282E-2</v>
       </c>
-      <c r="H30" s="46">
+      <c r="H30" s="45">
         <v>8.1021192667292116E-2</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="34">
         <v>8.4578436182628378E-2</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="34">
         <v>7.6788408641279601E-2</v>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="34">
         <v>8.0796012497066694E-2</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="34">
         <v>8.0720952440324886E-2</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="34">
         <v>7.9435124526223741E-2</v>
       </c>
     </row>
@@ -2230,19 +2233,19 @@
       <c r="H31" s="7">
         <v>0.25</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="34">
         <v>0.25</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="34">
         <v>0.25</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="34">
         <v>0.25</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="34">
         <v>0.25</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="34">
         <v>0.25</v>
       </c>
     </row>
@@ -2250,37 +2253,37 @@
       <c r="B32" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <v>76065601</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="22">
         <v>119952578</v>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="22">
         <v>243693689</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="22">
         <v>283201865</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="22">
         <v>309371619</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="22">
         <v>321587316</v>
       </c>
-      <c r="I32" s="34">
+      <c r="I32" s="33">
         <v>337520037.983904</v>
       </c>
-      <c r="J32" s="34">
+      <c r="J32" s="33">
         <v>352182583.47400075</v>
       </c>
-      <c r="K32" s="34">
+      <c r="K32" s="33">
         <v>366049420.51570606</v>
       </c>
-      <c r="L32" s="34">
+      <c r="L32" s="33">
         <v>379717705.8777625</v>
       </c>
-      <c r="M32" s="34">
+      <c r="M32" s="33">
         <v>393896365.01523811</v>
       </c>
     </row>
@@ -2288,37 +2291,37 @@
       <c r="B33" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <v>4.5436672423578184E-2</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="11">
         <v>0.71761329065988178</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="11">
         <v>0.19626332607774399</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="11">
         <v>0.22124904286003799</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="11">
         <v>-6.2686764968029829E-2</v>
       </c>
-      <c r="I33" s="48">
+      <c r="I33" s="47">
         <v>4.9544000000000032E-2</v>
       </c>
-      <c r="J33" s="48">
+      <c r="J33" s="47">
         <v>4.3441999999999981E-2</v>
       </c>
-      <c r="K33" s="48">
+      <c r="K33" s="47">
         <v>3.937400000000002E-2</v>
       </c>
-      <c r="L33" s="48">
+      <c r="L33" s="47">
         <v>3.7339999999999929E-2</v>
       </c>
-      <c r="M33" s="48">
+      <c r="M33" s="47">
         <v>3.7339999999999929E-2</v>
       </c>
     </row>
@@ -2326,37 +2329,37 @@
       <c r="B34" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="11">
         <v>0.57696220660900321</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="11">
         <v>1.0315835896415666</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="11">
         <v>0.16212227802091328</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="11">
         <v>9.2406714906344334E-2</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="11">
         <v>3.9485512728948846E-2</v>
       </c>
-      <c r="I34" s="48">
+      <c r="I34" s="47">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="J34" s="48">
+      <c r="J34" s="47">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="K34" s="48">
+      <c r="K34" s="47">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="L34" s="48">
+      <c r="L34" s="47">
         <v>0.02</v>
       </c>
-      <c r="M34" s="48">
+      <c r="M34" s="47">
         <v>0.02</v>
       </c>
     </row>
@@ -2364,37 +2367,37 @@
       <c r="B35" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="11">
         <v>1.779847532747483E-2</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="11">
         <v>1.5047816851752776E-2</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="11">
         <v>1.5489894460970446E-2</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="11">
         <v>1.731682763052677E-2</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="11">
         <v>1.5614735874719636E-2</v>
       </c>
-      <c r="I35" s="48">
+      <c r="I35" s="47">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="J35" s="48">
+      <c r="J35" s="47">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="K35" s="48">
+      <c r="K35" s="47">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="L35" s="48">
+      <c r="L35" s="47">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="M35" s="48">
+      <c r="M35" s="47">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
@@ -2402,37 +2405,37 @@
       <c r="B36" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="11">
         <v>0.60502972953569389</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="11">
         <v>1.0621544874175193</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="11">
         <v>0.18012342945819992</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="11">
         <v>0.11132373369080728</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="11">
         <v>5.5716804455808955E-2</v>
       </c>
-      <c r="I36" s="48">
+      <c r="I36" s="47">
         <v>4.9544000000000032E-2</v>
       </c>
-      <c r="J36" s="48">
+      <c r="J36" s="47">
         <v>4.3441999999999981E-2</v>
       </c>
-      <c r="K36" s="48">
+      <c r="K36" s="47">
         <v>3.937400000000002E-2</v>
       </c>
-      <c r="L36" s="48">
+      <c r="L36" s="47">
         <v>3.7339999999999929E-2</v>
       </c>
-      <c r="M36" s="48">
+      <c r="M36" s="47">
         <v>3.7339999999999929E-2</v>
       </c>
     </row>
@@ -2505,302 +2508,302 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="16">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="41"/>
+      <c r="L3" s="40"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="40"/>
+      <c r="N3" s="39"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="40"/>
+      <c r="P3" s="39"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
+      <c r="P5" s="51"/>
     </row>
     <row r="6" spans="1:17" ht="16">
-      <c r="C6" s="36">
+      <c r="C6" s="35">
         <v>2025</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="77" t="s">
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="77" t="s">
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="N6" s="78"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="78"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="77"/>
+      <c r="P6" s="77"/>
     </row>
     <row r="7" spans="1:17" ht="16">
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="64" t="s">
+      <c r="H7" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="J7" s="64" t="s">
+      <c r="J7" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="64" t="s">
+      <c r="K7" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="L7" s="64" t="s">
+      <c r="L7" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="64" t="s">
+      <c r="M7" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="N7" s="64" t="s">
+      <c r="N7" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="O7" s="64" t="s">
+      <c r="O7" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="P7" s="64" t="s">
+      <c r="P7" s="63" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="16">
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
-      <c r="K8" s="75"/>
-      <c r="L8" s="75"/>
-      <c r="M8" s="75" t="s">
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="N8" s="75" t="s">
+      <c r="N8" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="O8" s="75" t="s">
+      <c r="O8" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="P8" s="75" t="s">
+      <c r="P8" s="74" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="65">
         <v>23.82</v>
       </c>
-      <c r="E9" s="66">
+      <c r="E9" s="65">
         <v>1499074627</v>
       </c>
-      <c r="F9" s="66">
+      <c r="F9" s="65">
         <f t="shared" ref="F9:F14" si="0">D9*E9</f>
         <v>35707957615.139999</v>
       </c>
-      <c r="G9" s="67">
+      <c r="G9" s="66">
         <v>4231575000</v>
       </c>
-      <c r="H9" s="67">
+      <c r="H9" s="66">
         <f>F9+G9</f>
         <v>39939532615.139999</v>
       </c>
-      <c r="I9" s="67">
+      <c r="I9" s="66">
         <v>5357335000</v>
       </c>
-      <c r="J9" s="67">
+      <c r="J9" s="66">
         <v>2732722000</v>
       </c>
-      <c r="K9" s="66">
+      <c r="K9" s="65">
         <v>3401061000</v>
       </c>
-      <c r="L9" s="66">
+      <c r="L9" s="65">
         <v>2028489000</v>
       </c>
-      <c r="M9" s="68">
+      <c r="M9" s="67">
         <f>H9/(I9)</f>
         <v>7.455112031474604</v>
       </c>
-      <c r="N9" s="68">
+      <c r="N9" s="67">
         <f t="shared" ref="N9:N14" si="1">H9/(J9)</f>
         <v>14.615292962526009</v>
       </c>
-      <c r="O9" s="68">
+      <c r="O9" s="67">
         <f t="shared" ref="O9:O14" si="2">H9/(K9)</f>
         <v>11.74325677050191</v>
       </c>
-      <c r="P9" s="68">
+      <c r="P9" s="67">
         <f t="shared" ref="P9:P14" si="3">F9/(L9)</f>
         <v>17.603229603483182</v>
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="69">
+      <c r="D10" s="68">
         <v>111.4</v>
       </c>
-      <c r="E10" s="69">
+      <c r="E10" s="68">
         <v>99130435</v>
       </c>
-      <c r="F10" s="69">
+      <c r="F10" s="68">
         <f t="shared" si="0"/>
         <v>11043130459</v>
       </c>
-      <c r="G10" s="69">
+      <c r="G10" s="68">
         <v>8950000000</v>
       </c>
-      <c r="H10" s="69">
+      <c r="H10" s="68">
         <f>F10+G10</f>
         <v>19993130459</v>
       </c>
-      <c r="I10" s="69">
+      <c r="I10" s="68">
         <v>6704000000</v>
       </c>
-      <c r="J10" s="69">
+      <c r="J10" s="68">
         <f>K10-1116000000</f>
         <v>1206000000</v>
       </c>
-      <c r="K10" s="69">
+      <c r="K10" s="68">
         <v>2322000000</v>
       </c>
-      <c r="L10" s="69">
+      <c r="L10" s="68">
         <v>382000000</v>
       </c>
-      <c r="M10" s="70">
+      <c r="M10" s="69">
         <f t="shared" ref="M10:M12" si="4">H10/(I10)</f>
         <v>2.9822688632159906</v>
       </c>
-      <c r="N10" s="70">
+      <c r="N10" s="69">
         <f t="shared" si="1"/>
         <v>16.578051790215589</v>
       </c>
-      <c r="O10" s="70">
+      <c r="O10" s="69">
         <f t="shared" si="2"/>
         <v>8.610305968561585</v>
       </c>
-      <c r="P10" s="70">
+      <c r="P10" s="69">
         <f t="shared" si="3"/>
         <v>28.90871847905759</v>
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="69">
+      <c r="D11" s="68">
         <v>279.31</v>
       </c>
-      <c r="E11" s="69">
+      <c r="E11" s="68">
         <v>30701875</v>
       </c>
-      <c r="F11" s="69">
+      <c r="F11" s="68">
         <f t="shared" si="0"/>
         <v>8575340706.25</v>
       </c>
-      <c r="G11" s="69">
+      <c r="G11" s="68">
         <v>1245621389</v>
       </c>
-      <c r="H11" s="69">
+      <c r="H11" s="68">
         <f>G11+F11</f>
         <v>9820962095.25</v>
       </c>
-      <c r="I11" s="69">
+      <c r="I11" s="68">
         <v>1470909349.8</v>
       </c>
-      <c r="J11" s="69">
+      <c r="J11" s="68">
         <v>487288731</v>
       </c>
-      <c r="K11" s="69">
+      <c r="K11" s="68">
         <v>825631350</v>
       </c>
-      <c r="L11" s="69">
+      <c r="L11" s="68">
         <v>372586926</v>
       </c>
-      <c r="M11" s="70">
+      <c r="M11" s="69">
         <f t="shared" si="4"/>
         <v>6.6767962937929246</v>
       </c>
-      <c r="N11" s="70">
+      <c r="N11" s="69">
         <f t="shared" si="1"/>
         <v>20.154297586762784</v>
       </c>
-      <c r="O11" s="70">
+      <c r="O11" s="69">
         <f t="shared" si="2"/>
         <v>11.895093488455835</v>
       </c>
-      <c r="P11" s="70">
+      <c r="P11" s="69">
         <f t="shared" si="3"/>
         <v>23.015677974299077</v>
       </c>
@@ -2809,51 +2812,51 @@
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="69">
+      <c r="D12" s="68">
         <v>69.599999999999994</v>
       </c>
-      <c r="E12" s="69">
+      <c r="E12" s="68">
         <v>92347561</v>
       </c>
-      <c r="F12" s="69">
+      <c r="F12" s="68">
         <f t="shared" si="0"/>
         <v>6427390245.5999994</v>
       </c>
-      <c r="G12" s="53">
+      <c r="G12" s="52">
         <v>579074000</v>
       </c>
-      <c r="H12" s="69">
+      <c r="H12" s="68">
         <f>G12+F12</f>
         <v>7006464245.5999994</v>
       </c>
-      <c r="I12" s="69">
+      <c r="I12" s="68">
         <v>1913003000</v>
       </c>
-      <c r="J12" s="69">
+      <c r="J12" s="68">
         <v>476734000</v>
       </c>
-      <c r="K12" s="69">
+      <c r="K12" s="68">
         <v>867422000</v>
       </c>
-      <c r="L12" s="69">
+      <c r="L12" s="68">
         <v>180856000</v>
       </c>
-      <c r="M12" s="70">
+      <c r="M12" s="69">
         <f t="shared" si="4"/>
         <v>3.6625474427379356</v>
       </c>
-      <c r="N12" s="70">
+      <c r="N12" s="69">
         <f t="shared" si="1"/>
         <v>14.696799988253407</v>
       </c>
-      <c r="O12" s="70">
+      <c r="O12" s="69">
         <f t="shared" si="2"/>
         <v>8.0773421075324343</v>
       </c>
-      <c r="P12" s="70">
+      <c r="P12" s="69">
         <f t="shared" si="3"/>
         <v>35.538717242447028</v>
       </c>
@@ -2862,51 +2865,51 @@
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="69">
+      <c r="D13" s="68">
         <v>918.16</v>
       </c>
-      <c r="E13" s="69">
+      <c r="E13" s="68">
         <v>7772727</v>
       </c>
-      <c r="F13" s="69">
+      <c r="F13" s="68">
         <f t="shared" si="0"/>
         <v>7136607022.3199997</v>
       </c>
-      <c r="G13" s="53">
+      <c r="G13" s="52">
         <v>1182975138</v>
       </c>
-      <c r="H13" s="69">
+      <c r="H13" s="68">
         <f>G13+F13</f>
         <v>8319582160.3199997</v>
       </c>
-      <c r="I13" s="69">
+      <c r="I13" s="68">
         <v>1746487848</v>
       </c>
-      <c r="J13" s="69">
+      <c r="J13" s="68">
         <v>575559300</v>
       </c>
-      <c r="K13" s="69">
+      <c r="K13" s="68">
         <v>892250766</v>
       </c>
-      <c r="L13" s="69">
+      <c r="L13" s="68">
         <v>418284375</v>
       </c>
-      <c r="M13" s="70">
+      <c r="M13" s="69">
         <f>H13/(I13)</f>
         <v>4.763607241726425</v>
       </c>
-      <c r="N13" s="70">
+      <c r="N13" s="69">
         <f t="shared" si="1"/>
         <v>14.454778439545672</v>
       </c>
-      <c r="O13" s="70">
+      <c r="O13" s="69">
         <f t="shared" si="2"/>
         <v>9.3242645199589553</v>
       </c>
-      <c r="P13" s="70">
+      <c r="P13" s="69">
         <f t="shared" si="3"/>
         <v>17.061615132814847</v>
       </c>
@@ -2915,50 +2918,50 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="69">
+      <c r="D14" s="68">
         <v>22.49</v>
       </c>
-      <c r="E14" s="69">
+      <c r="E14" s="68">
         <v>163120000</v>
       </c>
-      <c r="F14" s="69">
+      <c r="F14" s="68">
         <f t="shared" si="0"/>
         <v>3668568799.9999995</v>
       </c>
-      <c r="G14" s="69">
+      <c r="G14" s="68">
         <v>616638906</v>
       </c>
-      <c r="H14" s="69">
+      <c r="H14" s="68">
         <v>3679110966</v>
       </c>
-      <c r="I14" s="53">
+      <c r="I14" s="52">
         <v>1608027543</v>
       </c>
-      <c r="J14" s="69">
+      <c r="J14" s="68">
         <v>401299861</v>
       </c>
-      <c r="K14" s="69">
+      <c r="K14" s="68">
         <v>601026839</v>
       </c>
-      <c r="L14" s="69">
+      <c r="L14" s="68">
         <v>160747463</v>
       </c>
-      <c r="M14" s="70">
+      <c r="M14" s="69">
         <f>H14/(I14)</f>
         <v>2.2879651421493095</v>
       </c>
-      <c r="N14" s="70">
+      <c r="N14" s="69">
         <f t="shared" si="1"/>
         <v>9.1679846507596974</v>
       </c>
-      <c r="O14" s="70">
+      <c r="O14" s="69">
         <f t="shared" si="2"/>
         <v>6.1213754981747162</v>
       </c>
-      <c r="P14" s="70">
+      <c r="P14" s="69">
         <f t="shared" si="3"/>
         <v>22.821939031162188</v>
       </c>
@@ -2967,150 +2970,150 @@
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="C15" s="73" t="s">
+      <c r="C15" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="74">
+      <c r="D15" s="73">
         <f t="shared" ref="D15:L15" si="5">SUM(D9:D14)/6</f>
         <v>237.46333333333334</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="73">
         <f t="shared" si="5"/>
         <v>315357870.83333331</v>
       </c>
-      <c r="F15" s="74">
+      <c r="F15" s="73">
         <f t="shared" si="5"/>
         <v>12093165808.051666</v>
       </c>
-      <c r="G15" s="74">
+      <c r="G15" s="73">
         <f t="shared" si="5"/>
         <v>2800980738.8333335</v>
       </c>
-      <c r="H15" s="74">
+      <c r="H15" s="73">
         <f t="shared" si="5"/>
         <v>14793130423.551666</v>
       </c>
-      <c r="I15" s="74">
+      <c r="I15" s="73">
         <f>SUM(I9:I13)/6</f>
         <v>2865289199.6333332</v>
       </c>
-      <c r="J15" s="74">
+      <c r="J15" s="73">
         <f t="shared" si="5"/>
         <v>979933982</v>
       </c>
-      <c r="K15" s="74">
+      <c r="K15" s="73">
         <f t="shared" si="5"/>
         <v>1484898659.1666667</v>
       </c>
-      <c r="L15" s="74">
+      <c r="L15" s="73">
         <f t="shared" si="5"/>
         <v>590493960.66666663</v>
       </c>
-      <c r="M15" s="74">
+      <c r="M15" s="73">
         <f t="shared" ref="M15:P15" si="6">SUM(M9:M14)/6</f>
         <v>4.638049502516199</v>
       </c>
-      <c r="N15" s="74">
+      <c r="N15" s="73">
         <f t="shared" si="6"/>
         <v>14.944534236343861</v>
       </c>
-      <c r="O15" s="74">
+      <c r="O15" s="73">
         <f t="shared" si="6"/>
         <v>9.2952730588642396</v>
       </c>
-      <c r="P15" s="74">
+      <c r="P15" s="73">
         <f t="shared" si="6"/>
         <v>24.158316243877319</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="69">
+      <c r="D16" s="68">
         <f t="shared" ref="D16:P16" si="7">MEDIAN(D9:D14)</f>
         <v>90.5</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E16" s="68">
         <f t="shared" si="7"/>
         <v>95738998</v>
       </c>
-      <c r="F16" s="69">
+      <c r="F16" s="68">
         <f t="shared" si="7"/>
         <v>7855973864.2849998</v>
       </c>
-      <c r="G16" s="69">
+      <c r="G16" s="68">
         <f t="shared" si="7"/>
         <v>1214298263.5</v>
       </c>
-      <c r="H16" s="69">
+      <c r="H16" s="68">
         <f t="shared" si="7"/>
         <v>9070272127.7849998</v>
       </c>
-      <c r="I16" s="69">
+      <c r="I16" s="68">
         <f>MEDIAN(I9:I13)</f>
         <v>1913003000</v>
       </c>
-      <c r="J16" s="69">
+      <c r="J16" s="68">
         <f t="shared" si="7"/>
         <v>531424015.5</v>
       </c>
-      <c r="K16" s="69">
+      <c r="K16" s="68">
         <f t="shared" si="7"/>
         <v>879836383</v>
       </c>
-      <c r="L16" s="69">
+      <c r="L16" s="68">
         <f t="shared" si="7"/>
         <v>377293463</v>
       </c>
-      <c r="M16" s="69">
+      <c r="M16" s="68">
         <f t="shared" si="7"/>
         <v>4.2130773422321806</v>
       </c>
-      <c r="N16" s="69">
+      <c r="N16" s="68">
         <f t="shared" si="7"/>
         <v>14.656046475389708</v>
       </c>
-      <c r="O16" s="69">
+      <c r="O16" s="68">
         <f t="shared" si="7"/>
         <v>8.9672852442602711</v>
       </c>
-      <c r="P16" s="69">
+      <c r="P16" s="68">
         <f t="shared" si="7"/>
         <v>22.918808502730634</v>
       </c>
     </row>
     <row r="17" spans="3:16">
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="51"/>
+      <c r="M17" s="51"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="51"/>
+      <c r="P17" s="51"/>
     </row>
     <row r="18" spans="3:16">
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="52"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="51"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="51"/>
+      <c r="P18" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3136,15 +3139,15 @@
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="18"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="17"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -3154,48 +3157,48 @@
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="18"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="17"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="16">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="18"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="17"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="40"/>
+      <c r="N3" s="39"/>
     </row>
     <row r="6" spans="1:14" ht="16">
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="37">
         <v>2025</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16">
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="8">
@@ -3203,7 +3206,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="16">
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D8">
@@ -3211,7 +3214,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="16">
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="8">
@@ -3219,78 +3222,78 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="16">
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>D7+D8*D9</f>
         <v>8.0085000000000003E-2</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16">
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f>155737000/3899375000</f>
         <v>3.9938964577656673E-2</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16">
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16">
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>9.7194915000000007E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16">
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f>1-D13</f>
         <v>0.90280508500000001</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16">
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <f>D14*D10+D13*D11*(1-D12)</f>
         <v>7.5212543432710013E-2</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16">
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
     <row r="17" spans="3:4" ht="16">
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>3844276000</v>
       </c>
     </row>
     <row r="18" spans="3:4" ht="16">
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="89">
+      <c r="D18" s="88">
         <v>1499074627</v>
       </c>
     </row>
@@ -3350,13 +3353,13 @@
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="16">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -3365,112 +3368,112 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
     </row>
     <row r="7" spans="1:15" ht="16">
-      <c r="E7" s="85" t="s">
+      <c r="E7" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="86"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="16">
-      <c r="D8" s="45">
+      <c r="D8" s="44">
         <v>2025</v>
       </c>
-      <c r="E8" s="76">
+      <c r="E8" s="75">
         <v>2026</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="75">
         <v>2027</v>
       </c>
-      <c r="G8" s="76">
+      <c r="G8" s="75">
         <v>2028</v>
       </c>
-      <c r="H8" s="76">
+      <c r="H8" s="75">
         <v>2029</v>
       </c>
-      <c r="I8" s="76">
+      <c r="I8" s="75">
         <v>2030</v>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="75">
         <v>2031</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="16">
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:15">
       <c r="C10" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>1967979500</v>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="85">
         <v>2189913698.1202202</v>
       </c>
-      <c r="F10" s="86">
+      <c r="F10" s="85">
         <v>2280569569.5538578</v>
       </c>
-      <c r="G10" s="86">
+      <c r="G10" s="85">
         <v>2288676984.0395546</v>
       </c>
-      <c r="H10" s="86">
+      <c r="H10" s="85">
         <v>2350781347.024569</v>
       </c>
-      <c r="I10" s="86">
+      <c r="I10" s="85">
         <v>2363393493.189096</v>
       </c>
-      <c r="J10" s="86">
+      <c r="J10" s="85">
         <v>2404752879.3199053</v>
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="D11" s="15"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="87"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
     </row>
     <row r="12" spans="1:15">
       <c r="C12" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <v>7.5212543432710013E-2</v>
       </c>
-      <c r="E12" s="87">
+      <c r="E12" s="86">
         <v>7.5212543432710013E-2</v>
       </c>
-      <c r="F12" s="87">
+      <c r="F12" s="86">
         <v>7.5212543432710013E-2</v>
       </c>
-      <c r="G12" s="87">
+      <c r="G12" s="86">
         <v>7.5212543432710013E-2</v>
       </c>
-      <c r="H12" s="87">
+      <c r="H12" s="86">
         <v>7.5212543432710013E-2</v>
       </c>
-      <c r="I12" s="87">
+      <c r="I12" s="86">
         <v>7.5212543432710013E-2</v>
       </c>
-      <c r="J12" s="87">
+      <c r="J12" s="86">
         <v>7.5212543432710013E-2</v>
       </c>
     </row>
@@ -3478,25 +3481,25 @@
       <c r="C13" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="E13" s="88">
+      <c r="E13" s="87">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="F13" s="88">
+      <c r="F13" s="87">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="G13" s="88">
+      <c r="G13" s="87">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="H13" s="88">
+      <c r="H13" s="87">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="I13" s="88">
+      <c r="I13" s="87">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="J13" s="88">
+      <c r="J13" s="87">
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
@@ -3504,229 +3507,223 @@
       <c r="C14" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>1</v>
       </c>
-      <c r="E14" s="86">
+      <c r="E14" s="85">
         <f>1/(1+E12)</f>
         <v>0.93004867373236977</v>
       </c>
-      <c r="F14" s="86">
+      <c r="F14" s="85">
         <f xml:space="preserve"> 1 /(1 + $E$12)^2</f>
         <v>0.86499053551133998</v>
       </c>
-      <c r="G14" s="86">
+      <c r="G14" s="85">
         <f xml:space="preserve"> 1 /(1 + $E$12)^3</f>
         <v>0.80448330034337401</v>
       </c>
-      <c r="H14" s="86">
+      <c r="H14" s="85">
         <f xml:space="preserve"> 1 /(1 + $E$12)^4</f>
         <v>0.74820862652419473</v>
       </c>
-      <c r="I14" s="86">
+      <c r="I14" s="85">
         <f xml:space="preserve"> 1 /(1 + $E$12)^5</f>
         <v>0.69587044077394533</v>
       </c>
-      <c r="J14" s="86"/>
+      <c r="J14" s="85"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="D15" s="10"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="87"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="86"/>
     </row>
     <row r="16" spans="1:15">
       <c r="C16" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="86">
+      <c r="D16" s="9"/>
+      <c r="E16" s="85">
         <f>E14*E10</f>
         <v>2036726330.5250599</v>
       </c>
-      <c r="F16" s="86">
+      <c r="F16" s="85">
         <f t="shared" ref="F16:I16" si="0">F14*F10</f>
         <v>1972671093.2392576</v>
       </c>
-      <c r="G16" s="86">
+      <c r="G16" s="85">
         <f>G14*G10</f>
         <v>1841202413.5400605</v>
       </c>
-      <c r="H16" s="86">
+      <c r="H16" s="85">
         <f t="shared" si="0"/>
         <v>1758874882.9159491</v>
       </c>
-      <c r="I16" s="86">
+      <c r="I16" s="85">
         <f t="shared" si="0"/>
         <v>1644615671.8277705</v>
       </c>
-      <c r="J16" s="87"/>
-    </row>
-    <row r="17" spans="3:10">
-      <c r="D17" s="10"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="86"/>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86">
+      <c r="J16" s="86"/>
+    </row>
+    <row r="17" spans="3:10" ht="16">
+      <c r="D17" s="9"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="86"/>
+    </row>
+    <row r="18" spans="3:10">
+      <c r="C18" s="92" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="85">
         <f>I10*(1+I13)/(I12-I13)</f>
         <v>41667768153.793617</v>
       </c>
-      <c r="J17" s="87"/>
-    </row>
-    <row r="18" spans="3:10">
-      <c r="C18" s="93" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86">
-        <f>I11*(1+I14)/(I13-I14)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="87"/>
+      <c r="J18" s="86"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86">
-        <f>I18*I15</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="86"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="85"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="85"/>
     </row>
     <row r="20" spans="3:10">
       <c r="C20" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="10">
-        <f>SUM(E16:I16)+(I17/(1+D12)^5)</f>
+      <c r="D20" s="9">
+        <f>SUM(E16:I16)+(I18/(1+D12)^5)</f>
         <v>38249458583.295029</v>
       </c>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
     </row>
     <row r="21" spans="3:10">
       <c r="C21" t="s">
         <v>105</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>4231575000</v>
       </c>
-      <c r="E21" s="86"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="86"/>
-      <c r="H21" s="86"/>
-      <c r="I21" s="86"/>
-      <c r="J21" s="86"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="85"/>
     </row>
     <row r="22" spans="3:10">
       <c r="C22" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <f>D20-D21</f>
         <v>34017883583.295029</v>
       </c>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="86"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="85"/>
     </row>
     <row r="23" spans="3:10">
-      <c r="C23" s="91" t="s">
+      <c r="C23" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="92">
+      <c r="D23" s="91">
         <f>D22/1499074627</f>
         <v>22.692588461304823</v>
       </c>
-      <c r="E23" s="86"/>
-      <c r="F23" s="86"/>
-      <c r="G23" s="86"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="86"/>
-      <c r="J23" s="86"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
     </row>
     <row r="28" spans="3:10" ht="16">
-      <c r="E28" s="51" t="s">
+      <c r="E28" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50"/>
     </row>
     <row r="29" spans="3:10" ht="16">
-      <c r="C29" s="22"/>
-      <c r="D29" s="44">
+      <c r="C29" s="21"/>
+      <c r="D29" s="43">
         <v>2025</v>
       </c>
-      <c r="E29" s="45">
+      <c r="E29" s="44">
         <v>2026</v>
       </c>
-      <c r="F29" s="45">
+      <c r="F29" s="44">
         <v>2027</v>
       </c>
-      <c r="G29" s="45">
+      <c r="G29" s="44">
         <v>2028</v>
       </c>
-      <c r="H29" s="45">
+      <c r="H29" s="44">
         <v>2029</v>
       </c>
-      <c r="I29" s="45">
+      <c r="I29" s="44">
         <v>2030</v>
       </c>
     </row>
     <row r="30" spans="3:10" ht="16">
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
     </row>
     <row r="31" spans="3:10">
       <c r="C31" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>2049541.5</v>
       </c>
-      <c r="E31" s="86">
+      <c r="E31" s="85">
         <v>2192875.9340436002</v>
       </c>
-      <c r="F31" s="86">
+      <c r="F31" s="85">
         <v>2244136.1801708927</v>
       </c>
-      <c r="G31" s="86">
+      <c r="G31" s="85">
         <v>2286761.5667930804</v>
       </c>
-      <c r="H31" s="86">
+      <c r="H31" s="85">
         <v>2324706.2588231913</v>
       </c>
-      <c r="I31" s="86">
+      <c r="I31" s="85">
         <v>2340844.4645579113</v>
       </c>
     </row>
@@ -3734,22 +3731,22 @@
       <c r="C32" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>59877</v>
       </c>
-      <c r="E32" s="86">
+      <c r="E32" s="85">
         <v>38904.568882927357</v>
       </c>
-      <c r="F32" s="86">
+      <c r="F32" s="85">
         <v>-23474.832539672789</v>
       </c>
-      <c r="G32" s="86">
+      <c r="G32" s="85">
         <v>39533.285517480224</v>
       </c>
-      <c r="H32" s="86">
+      <c r="H32" s="85">
         <v>16798.978092028003</v>
       </c>
-      <c r="I32" s="86">
+      <c r="I32" s="85">
         <v>9962.700043230725</v>
       </c>
     </row>
@@ -3757,22 +3754,22 @@
       <c r="C33" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>690024</v>
       </c>
-      <c r="E33" s="86">
+      <c r="E33" s="85">
         <v>706116.0082552057</v>
       </c>
-      <c r="F33" s="86">
+      <c r="F33" s="85">
         <v>751698.28525655984</v>
       </c>
-      <c r="G33" s="86">
+      <c r="G33" s="85">
         <v>777507.56252788869</v>
       </c>
-      <c r="H33" s="86">
+      <c r="H33" s="85">
         <v>803801.82309710362</v>
       </c>
-      <c r="I33" s="86">
+      <c r="I33" s="85">
         <v>861082.278241514</v>
       </c>
     </row>
@@ -3780,22 +3777,22 @@
       <c r="C34" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <v>668339</v>
       </c>
-      <c r="E34" s="86">
+      <c r="E34" s="85">
         <v>767748.01915557403</v>
       </c>
-      <c r="F34" s="86">
+      <c r="F34" s="85">
         <v>762372.95078261325</v>
       </c>
-      <c r="G34" s="86">
+      <c r="G34" s="85">
         <v>818836.19398109755</v>
       </c>
-      <c r="H34" s="86">
+      <c r="H34" s="85">
         <v>845041.32646490843</v>
       </c>
-      <c r="I34" s="86">
+      <c r="I34" s="85">
         <v>861082.278241514</v>
       </c>
     </row>
@@ -3803,26 +3800,26 @@
       <c r="C35" t="s">
         <v>58</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>11800006</v>
       </c>
-      <c r="E35" s="86">
+      <c r="E35" s="85">
         <f>D35+E33-E34</f>
         <v>11738373.989099633</v>
       </c>
-      <c r="F35" s="86">
+      <c r="F35" s="85">
         <f t="shared" ref="F35:I35" si="1">E35+F33-F34</f>
         <v>11727699.323573578</v>
       </c>
-      <c r="G35" s="86">
+      <c r="G35" s="85">
         <f t="shared" si="1"/>
         <v>11686370.69212037</v>
       </c>
-      <c r="H35" s="86">
+      <c r="H35" s="85">
         <f t="shared" si="1"/>
         <v>11645131.188752566</v>
       </c>
-      <c r="I35" s="86">
+      <c r="I35" s="85">
         <f t="shared" si="1"/>
         <v>11645131.188752566</v>
       </c>
@@ -3831,27 +3828,27 @@
       <c r="C36" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <f>D35+D32</f>
         <v>11859883</v>
       </c>
-      <c r="E36" s="86">
+      <c r="E36" s="85">
         <f t="shared" ref="E36:I36" si="2">E35+E32</f>
         <v>11777278.55798256</v>
       </c>
-      <c r="F36" s="86">
+      <c r="F36" s="85">
         <f t="shared" si="2"/>
         <v>11704224.491033906</v>
       </c>
-      <c r="G36" s="86">
+      <c r="G36" s="85">
         <f t="shared" si="2"/>
         <v>11725903.97763785</v>
       </c>
-      <c r="H36" s="86">
+      <c r="H36" s="85">
         <f t="shared" si="2"/>
         <v>11661930.166844593</v>
       </c>
-      <c r="I36" s="86">
+      <c r="I36" s="85">
         <f t="shared" si="2"/>
         <v>11655093.888795797</v>
       </c>
@@ -3860,27 +3857,27 @@
       <c r="C37" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="11">
         <f>D31/((D36+11728774)/2)</f>
         <v>0.17377347934645029</v>
       </c>
-      <c r="E37" s="88">
+      <c r="E37" s="87">
         <f>E31/((E36+D36)/2)</f>
         <v>0.1855447769110872</v>
       </c>
-      <c r="F37" s="88">
+      <c r="F37" s="87">
         <f t="shared" ref="F37:I37" si="3">F31/((F36+E36)/2)</f>
         <v>0.19114076092031845</v>
       </c>
-      <c r="G37" s="88">
+      <c r="G37" s="87">
         <f t="shared" si="3"/>
         <v>0.19519838056805294</v>
       </c>
-      <c r="H37" s="88">
+      <c r="H37" s="87">
         <f t="shared" si="3"/>
         <v>0.19879619843906121</v>
       </c>
-      <c r="I37" s="88">
+      <c r="I37" s="87">
         <f t="shared" si="3"/>
         <v>0.20078415315539896</v>
       </c>
@@ -3889,22 +3886,22 @@
       <c r="C38" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="14">
         <v>6.6153000000000003E-2</v>
       </c>
-      <c r="E38" s="87">
+      <c r="E38" s="86">
         <v>6.6153000000000003E-2</v>
       </c>
-      <c r="F38" s="87">
+      <c r="F38" s="86">
         <v>6.6153000000000003E-2</v>
       </c>
-      <c r="G38" s="87">
+      <c r="G38" s="86">
         <v>6.6153000000000003E-2</v>
       </c>
-      <c r="H38" s="87">
+      <c r="H38" s="86">
         <v>6.6153000000000003E-2</v>
       </c>
-      <c r="I38" s="87">
+      <c r="I38" s="86">
         <v>6.6153000000000003E-2</v>
       </c>
     </row>
@@ -3912,27 +3909,27 @@
       <c r="C39" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="14">
         <f>D37-D38</f>
         <v>0.10762047934645029</v>
       </c>
-      <c r="E39" s="87">
+      <c r="E39" s="86">
         <f t="shared" ref="E39:I39" si="4">E37-E38</f>
         <v>0.1193917769110872</v>
       </c>
-      <c r="F39" s="87">
+      <c r="F39" s="86">
         <f t="shared" si="4"/>
         <v>0.12498776092031845</v>
       </c>
-      <c r="G39" s="87">
+      <c r="G39" s="86">
         <f t="shared" si="4"/>
         <v>0.12904538056805293</v>
       </c>
-      <c r="H39" s="87">
+      <c r="H39" s="86">
         <f t="shared" si="4"/>
         <v>0.13264319843906119</v>
       </c>
-      <c r="I39" s="87">
+      <c r="I39" s="86">
         <f t="shared" si="4"/>
         <v>0.13463115315539897</v>
       </c>
@@ -3945,30 +3942,30 @@
       <c r="I40" s="95"/>
     </row>
     <row r="41" spans="3:9">
-      <c r="C41" s="81" t="s">
+      <c r="C41" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="D41" s="82">
+      <c r="D41" s="81">
         <f>D33-D34+D32</f>
         <v>81562</v>
       </c>
-      <c r="E41" s="90">
+      <c r="E41" s="89">
         <f t="shared" ref="E41:I41" si="5">E33-E34+E32</f>
         <v>-22727.442017440975</v>
       </c>
-      <c r="F41" s="90">
+      <c r="F41" s="89">
         <f t="shared" si="5"/>
         <v>-34149.498065726191</v>
       </c>
-      <c r="G41" s="90">
+      <c r="G41" s="89">
         <f t="shared" si="5"/>
         <v>-1795.3459357286338</v>
       </c>
-      <c r="H41" s="90">
+      <c r="H41" s="89">
         <f t="shared" si="5"/>
         <v>-24440.525275776803</v>
       </c>
-      <c r="I41" s="90">
+      <c r="I41" s="89">
         <f t="shared" si="5"/>
         <v>9962.700043230725</v>
       </c>
@@ -3977,27 +3974,27 @@
       <c r="C42" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="11">
         <f>D41/D31</f>
         <v>3.979524200900543E-2</v>
       </c>
-      <c r="E42" s="88">
+      <c r="E42" s="87">
         <f t="shared" ref="E42:I42" si="6">E41/E31</f>
         <v>-1.0364216992218171E-2</v>
       </c>
-      <c r="F42" s="88">
+      <c r="F42" s="87">
         <f t="shared" si="6"/>
         <v>-1.5217212915806954E-2</v>
       </c>
-      <c r="G42" s="88">
+      <c r="G42" s="87">
         <f t="shared" si="6"/>
         <v>-7.85104123577868E-4</v>
       </c>
-      <c r="H42" s="88">
+      <c r="H42" s="87">
         <f t="shared" si="6"/>
         <v>-1.0513382145815292E-2</v>
       </c>
-      <c r="I42" s="88">
+      <c r="I42" s="87">
         <f t="shared" si="6"/>
         <v>4.2560281958384056E-3</v>
       </c>
@@ -4006,7 +4003,7 @@
       <c r="C43" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="94">
+      <c r="D43" s="93">
         <f>D42*D37</f>
         <v>6.9153576653388964E-3</v>
       </c>
@@ -4035,27 +4032,27 @@
       <c r="C44" t="s">
         <v>59</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="11">
         <f>D37-D42</f>
         <v>0.13397823733744485</v>
       </c>
-      <c r="E44" s="88">
+      <c r="E44" s="87">
         <f t="shared" ref="E44:I44" si="8">E37-E42</f>
         <v>0.19590899390330538</v>
       </c>
-      <c r="F44" s="88">
+      <c r="F44" s="87">
         <f t="shared" si="8"/>
         <v>0.20635797383612542</v>
       </c>
-      <c r="G44" s="88">
+      <c r="G44" s="87">
         <f t="shared" si="8"/>
         <v>0.19598348469163082</v>
       </c>
-      <c r="H44" s="88">
+      <c r="H44" s="87">
         <f t="shared" si="8"/>
         <v>0.2093095805848765</v>
       </c>
-      <c r="I44" s="88">
+      <c r="I44" s="87">
         <f t="shared" si="8"/>
         <v>0.19652812495956057</v>
       </c>
@@ -4064,16 +4061,16 @@
       <c r="C45" t="s">
         <v>57</v>
       </c>
-      <c r="D45" s="94">
+      <c r="D45" s="93">
         <v>-6.6879206038194555E-2</v>
       </c>
-      <c r="E45" s="88">
+      <c r="E45" s="87">
         <v>4.7205262475894391E-2</v>
       </c>
-      <c r="F45" s="88">
+      <c r="F45" s="87">
         <v>4.1633363426045726E-2</v>
       </c>
-      <c r="G45" s="88">
+      <c r="G45" s="87">
         <v>3.7882417686030199E-2</v>
       </c>
       <c r="H45" s="97">
@@ -4084,16 +4081,16 @@
       </c>
     </row>
     <row r="51" spans="3:4" ht="16">
-      <c r="C51" s="36" t="s">
+      <c r="C51" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="D51" s="36"/>
+      <c r="D51" s="35"/>
     </row>
     <row r="52" spans="3:4">
       <c r="C52" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="9">
         <v>38249458583.295029</v>
       </c>
     </row>
@@ -4101,12 +4098,12 @@
       <c r="C53" s="99" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="9">
         <v>4231575000</v>
       </c>
     </row>
     <row r="54" spans="3:4">
-      <c r="C54" s="91" t="s">
+      <c r="C54" s="90" t="s">
         <v>9</v>
       </c>
       <c r="D54" s="98">
@@ -4130,7 +4127,7 @@
       </c>
     </row>
     <row r="58" spans="3:4">
-      <c r="C58" s="91" t="s">
+      <c r="C58" s="90" t="s">
         <v>108</v>
       </c>
       <c r="D58" s="100">
@@ -4204,13 +4201,13 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16" ht="16">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -4224,262 +4221,262 @@
       <c r="P3" s="1"/>
     </row>
     <row r="6" spans="1:16" ht="16">
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
     </row>
     <row r="7" spans="1:16">
       <c r="C7" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="101">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="101">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="101">
         <v>0.02</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="C8" s="33">
+      <c r="C8" s="32">
         <v>0.06</v>
       </c>
-      <c r="D8" s="84">
+      <c r="D8" s="83">
         <v>30.184208510389791</v>
       </c>
-      <c r="E8" s="84">
+      <c r="E8" s="83">
         <v>31.816613395791673</v>
       </c>
-      <c r="F8" s="84">
+      <c r="F8" s="83">
         <v>33.653068891868791</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="C9" s="33">
+      <c r="C9" s="32">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="D9" s="84">
+      <c r="D9" s="83">
         <v>26.883097803525107</v>
       </c>
-      <c r="E9" s="84">
+      <c r="E9" s="83">
         <v>28.173100878922686</v>
       </c>
-      <c r="F9" s="84">
+      <c r="F9" s="83">
         <v>29.606437629364436</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="C10" s="33">
+      <c r="C10" s="32">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D10" s="84">
+      <c r="D10" s="83">
         <v>24.18216077625198</v>
       </c>
-      <c r="E10" s="84">
+      <c r="E10" s="83">
         <v>25.223508296265294</v>
       </c>
-      <c r="F10" s="84">
+      <c r="F10" s="83">
         <v>26.368990568279937</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="C11" s="33">
+      <c r="C11" s="32">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="D11" s="84">
+      <c r="D11" s="83">
         <v>21.931355091807173</v>
       </c>
-      <c r="E11" s="84">
+      <c r="E11" s="83">
         <v>22.786815350323913</v>
       </c>
-      <c r="F11" s="84">
+      <c r="F11" s="83">
         <v>23.720044723251259</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="C12" s="33">
+      <c r="C12" s="32">
         <v>0.08</v>
       </c>
-      <c r="D12" s="84">
+      <c r="D12" s="83">
         <v>20.026805248137808</v>
       </c>
-      <c r="E12" s="84">
+      <c r="E12" s="83">
         <v>20.739928167739464</v>
       </c>
-      <c r="F12" s="84">
+      <c r="F12" s="83">
         <v>21.512477997307922</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="C13" s="33">
+      <c r="C13" s="32">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="D13" s="84">
+      <c r="D13" s="83">
         <v>18.394314424079131</v>
       </c>
-      <c r="E13" s="84">
+      <c r="E13" s="83">
         <v>18.996225070607601</v>
       </c>
-      <c r="F13" s="84">
+      <c r="F13" s="83">
         <v>19.644436536099796</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
     </row>
     <row r="17" spans="3:13" ht="16">
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="79" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="15"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="14"/>
     </row>
     <row r="18" spans="3:13">
       <c r="C18" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <v>2.3E-2</v>
       </c>
       <c r="E18" s="7">
         <f>POWER(('Operating Forecast'!M8/'Operating Forecast'!H8),1/5)-1</f>
         <v>3.9499418413377896E-2</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="11">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="15"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="14"/>
     </row>
     <row r="19" spans="3:13">
       <c r="C19" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="E19" s="7">
         <f>POWER(('Operating Forecast'!M10/'Operating Forecast'!H10),1/5)-1</f>
         <v>3.5259451640203388E-2</v>
       </c>
-      <c r="F19" s="79">
+      <c r="F19" s="78">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="15"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="14"/>
     </row>
     <row r="20" spans="3:13">
       <c r="C20" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="48">
         <v>8.6</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="48">
         <v>9.3000000000000007</v>
       </c>
       <c r="F20">
         <v>10</v>
       </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="15"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="14"/>
     </row>
     <row r="21" spans="3:13">
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
     </row>
     <row r="22" spans="3:13">
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
     </row>
     <row r="23" spans="3:13">
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
     </row>
     <row r="24" spans="3:13">
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
     </row>
     <row r="25" spans="3:13">
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
     </row>
     <row r="28" spans="3:13">
-      <c r="F28" s="10"/>
+      <c r="F28" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/AENA DCF VALUATION.xlsx
+++ b/AENA DCF VALUATION.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniomaria/Desktop/Finance &amp; Career /AENA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FADDC9-8435-CB48-ABBE-5D1E6253A812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDCD675-B1D5-0E46-855B-9AB3E49691F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="112">
   <si>
     <t>AENA</t>
   </si>
@@ -320,9 +320,6 @@
   </si>
   <si>
     <t>(EUR in thousands, fiscal year ending December 31)</t>
-  </si>
-  <si>
-    <t>(eur)</t>
   </si>
   <si>
     <t>Bear</t>
@@ -549,13 +546,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -611,6 +601,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -812,7 +808,7 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="3"/>
@@ -881,16 +877,16 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -898,7 +894,6 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -925,7 +920,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -970,29 +965,24 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="29" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="28" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1037,10 +1027,18 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="185" fontId="12" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="31" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="_x000a_386grabber=M" xfId="5" xr:uid="{B52C3E28-7C4F-4347-98B2-3507D3681DDE}"/>
@@ -1365,7 +1363,7 @@
     </row>
     <row r="7" spans="7:15" ht="34">
       <c r="G7" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="7:15" ht="34">
@@ -1526,50 +1524,50 @@
       <c r="M7" s="24"/>
     </row>
     <row r="8" spans="1:16" ht="16">
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="54">
         <v>2180616</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="54">
         <v>2318750</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="54">
         <v>4182169</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="54">
         <v>5039822</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="54">
         <v>5763531</v>
       </c>
-      <c r="H8" s="55">
+      <c r="H8" s="54">
         <v>6278337</v>
       </c>
-      <c r="I8" s="56">
+      <c r="I8" s="55">
         <f>H8*(1.05)</f>
         <v>6592253.8500000006</v>
       </c>
-      <c r="J8" s="56">
+      <c r="J8" s="55">
         <f>I8*(1+I9-0.55%)</f>
         <v>6885609.1463250006</v>
       </c>
-      <c r="K8" s="56">
+      <c r="K8" s="55">
         <f t="shared" ref="K8:M8" si="0">J8*(1+J9-0.55%)</f>
         <v>7154147.9030316751</v>
       </c>
-      <c r="L8" s="56">
+      <c r="L8" s="55">
         <f t="shared" si="0"/>
         <v>7393811.8577832356</v>
       </c>
-      <c r="M8" s="111">
+      <c r="M8" s="105">
         <f t="shared" si="0"/>
         <v>7600838.5898011643</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="16">
-      <c r="B9" s="112" t="s">
+      <c r="B9" s="106" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="34"/>
@@ -1609,13 +1607,13 @@
         <f t="shared" si="1"/>
         <v>3.3499999999999912E-2</v>
       </c>
-      <c r="M9" s="113">
+      <c r="M9" s="107">
         <f>(M8-L8)/L8</f>
         <v>2.7999999999999747E-2</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="16">
-      <c r="B10" s="80" t="s">
+      <c r="B10" s="79" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="34">
@@ -1658,13 +1656,13 @@
         <f t="shared" si="2"/>
         <v>4676968.6129946969</v>
       </c>
-      <c r="M10" s="114">
+      <c r="M10" s="108">
         <f t="shared" si="2"/>
         <v>4864321.9564948715</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16">
-      <c r="B11" s="115" t="s">
+      <c r="B11" s="109" t="s">
         <v>87</v>
       </c>
       <c r="C11" s="40">
@@ -1707,13 +1705,13 @@
         <f t="shared" si="3"/>
         <v>0.63255174772555212</v>
       </c>
-      <c r="M11" s="113">
+      <c r="M11" s="107">
         <f t="shared" si="3"/>
         <v>0.6399717477255521</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="16">
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="79" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="34">
@@ -1731,7 +1729,7 @@
       <c r="G12" s="34">
         <v>847811</v>
       </c>
-      <c r="H12" s="63">
+      <c r="H12" s="62">
         <v>796897</v>
       </c>
       <c r="I12" s="20">
@@ -1750,13 +1748,13 @@
         <f t="shared" si="4"/>
         <v>1251979.6583841993</v>
       </c>
-      <c r="M12" s="116">
+      <c r="M12" s="110">
         <f>M8*M28</f>
         <v>1367603.9778708487</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="16">
-      <c r="B13" s="115" t="s">
+      <c r="B13" s="109" t="s">
         <v>89</v>
       </c>
       <c r="C13" s="40">
@@ -1799,13 +1797,13 @@
         <f t="shared" si="5"/>
         <v>0.16932803842801047</v>
       </c>
-      <c r="M13" s="113">
+      <c r="M13" s="107">
         <f t="shared" si="5"/>
         <v>0.17992803842801047</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="16">
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="79" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="34">
@@ -1842,13 +1840,13 @@
         <f t="shared" si="6"/>
         <v>3424988.9546104977</v>
       </c>
-      <c r="M14" s="114">
+      <c r="M14" s="108">
         <f t="shared" si="6"/>
         <v>3496717.978624023</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16">
-      <c r="B15" s="115" t="s">
+      <c r="B15" s="109" t="s">
         <v>90</v>
       </c>
       <c r="C15" s="40">
@@ -1891,13 +1889,13 @@
         <f t="shared" si="7"/>
         <v>0.46322370929754164</v>
       </c>
-      <c r="M15" s="113">
+      <c r="M15" s="107">
         <f t="shared" si="7"/>
         <v>0.46004370929754163</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16">
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="79" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="34">
@@ -1940,13 +1938,13 @@
         <f t="shared" si="9"/>
         <v>2568741.7159578735</v>
       </c>
-      <c r="M16" s="114">
+      <c r="M16" s="108">
         <f>M14*(1-0.25)</f>
         <v>2622538.4839680172</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="16">
-      <c r="B17" s="115" t="s">
+      <c r="B17" s="109" t="s">
         <v>91</v>
       </c>
       <c r="C17" s="44">
@@ -1989,13 +1987,13 @@
         <f t="shared" si="10"/>
         <v>0.34741778197315626</v>
       </c>
-      <c r="M17" s="117">
+      <c r="M17" s="111">
         <f t="shared" si="10"/>
         <v>0.34503278197315618</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="16">
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="79" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="34">
@@ -2037,13 +2035,13 @@
         <f t="shared" si="11"/>
         <v>1312542.3930193011</v>
       </c>
-      <c r="M18" s="114">
+      <c r="M18" s="108">
         <f>M29*M8</f>
         <v>1366015.4249214039</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="16">
-      <c r="B19" s="115" t="s">
+      <c r="B19" s="109" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="40">
@@ -2086,13 +2084,13 @@
         <f t="shared" si="12"/>
         <v>0.17751904136397906</v>
       </c>
-      <c r="M19" s="113">
+      <c r="M19" s="107">
         <f t="shared" si="12"/>
         <v>0.17971904136397909</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="16">
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="79" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="36">
@@ -2129,13 +2127,13 @@
         <f t="shared" si="13"/>
         <v>-199352.18072273867</v>
       </c>
-      <c r="M20" s="114">
+      <c r="M20" s="108">
         <f t="shared" si="13"/>
         <v>-229256.72527033903</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="16">
-      <c r="B21" s="112" t="s">
+      <c r="B21" s="106" t="s">
         <v>92</v>
       </c>
       <c r="C21" s="37"/>
@@ -2175,56 +2173,56 @@
         <f t="shared" si="14"/>
         <v>-2.6962030486735584E-2</v>
       </c>
-      <c r="M21" s="113">
+      <c r="M21" s="107">
         <f t="shared" si="14"/>
         <v>-3.0162030486735585E-2</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="16">
-      <c r="B22" s="118" t="s">
+      <c r="B22" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="119">
+      <c r="C22" s="113">
         <f>C16+C12-C18-C20</f>
         <v>796410</v>
       </c>
-      <c r="D22" s="119">
+      <c r="D22" s="113">
         <f t="shared" ref="D22:L22" si="15">D16+D12-D18-D20</f>
         <v>479734</v>
       </c>
-      <c r="E22" s="119">
+      <c r="E22" s="113">
         <f t="shared" si="15"/>
         <v>937530.5</v>
       </c>
-      <c r="F22" s="119">
+      <c r="F22" s="113">
         <f t="shared" si="15"/>
         <v>1120722.5</v>
       </c>
-      <c r="G22" s="119">
+      <c r="G22" s="113">
         <f t="shared" si="15"/>
         <v>2073714.75</v>
       </c>
-      <c r="H22" s="119">
+      <c r="H22" s="113">
         <f t="shared" si="15"/>
         <v>2067637.25</v>
       </c>
-      <c r="I22" s="120">
+      <c r="I22" s="114">
         <f t="shared" si="15"/>
         <v>2231766.73172775</v>
       </c>
-      <c r="J22" s="120">
+      <c r="J22" s="114">
         <f t="shared" si="15"/>
         <v>2394531.2395730196</v>
       </c>
-      <c r="K22" s="120">
+      <c r="K22" s="114">
         <f t="shared" si="15"/>
         <v>2553843.4308428043</v>
       </c>
-      <c r="L22" s="120">
+      <c r="L22" s="114">
         <f t="shared" si="15"/>
         <v>2707531.1620455105</v>
       </c>
-      <c r="M22" s="121">
+      <c r="M22" s="115">
         <f>M16+M12-M18-M20</f>
         <v>2853383.7621878008</v>
       </c>
@@ -2310,79 +2308,79 @@
       <c r="M26" s="24"/>
     </row>
     <row r="27" spans="2:13" ht="16">
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="122">
+      <c r="C27" s="116">
         <f t="shared" ref="C27:G27" si="16">C14/C8</f>
         <v>-4.2323820425054205E-2</v>
       </c>
-      <c r="D27" s="122">
+      <c r="D27" s="116">
         <f t="shared" si="16"/>
         <v>-6.5457681940700813E-2</v>
       </c>
-      <c r="E27" s="122">
+      <c r="E27" s="116">
         <f t="shared" si="16"/>
         <v>0.30694072860278959</v>
       </c>
-      <c r="F27" s="122">
+      <c r="F27" s="116">
         <f t="shared" si="16"/>
         <v>0.43680471254738756</v>
       </c>
-      <c r="G27" s="122">
+      <c r="G27" s="116">
         <f t="shared" si="16"/>
         <v>0.46196003803918118</v>
       </c>
-      <c r="H27" s="122">
+      <c r="H27" s="116">
         <f>H14/H8</f>
         <v>0.47594370929754171</v>
       </c>
-      <c r="I27" s="123">
+      <c r="I27" s="117">
         <f>H27-0.318%</f>
         <v>0.47276370929754169</v>
       </c>
-      <c r="J27" s="123">
+      <c r="J27" s="117">
         <f t="shared" ref="J27:L27" si="17">I27-0.318%</f>
         <v>0.46958370929754167</v>
       </c>
-      <c r="K27" s="123">
+      <c r="K27" s="117">
         <f t="shared" si="17"/>
         <v>0.46640370929754166</v>
       </c>
-      <c r="L27" s="123">
+      <c r="L27" s="117">
         <f t="shared" si="17"/>
         <v>0.46322370929754164</v>
       </c>
-      <c r="M27" s="124">
+      <c r="M27" s="118">
         <f>L27-0.318%</f>
         <v>0.46004370929754163</v>
       </c>
     </row>
     <row r="28" spans="2:13" ht="16">
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="125">
+      <c r="C28" s="119">
         <f t="shared" ref="C28:G28" si="18">C12/C8</f>
         <v>0.37001608719737911</v>
       </c>
-      <c r="D28" s="125">
+      <c r="D28" s="119">
         <f t="shared" si="18"/>
         <v>0.34355536388140162</v>
       </c>
-      <c r="E28" s="125">
+      <c r="E28" s="119">
         <f t="shared" si="18"/>
         <v>0.19013459283926595</v>
       </c>
-      <c r="F28" s="125">
+      <c r="F28" s="119">
         <f t="shared" si="18"/>
         <v>0.16294067528575415</v>
       </c>
-      <c r="G28" s="125">
+      <c r="G28" s="119">
         <f t="shared" si="18"/>
         <v>0.14709923482670606</v>
       </c>
-      <c r="H28" s="125">
+      <c r="H28" s="119">
         <f>H12/H8</f>
         <v>0.12692803842801048</v>
       </c>
@@ -2402,36 +2400,36 @@
         <f t="shared" si="19"/>
         <v>0.16932803842801047</v>
       </c>
-      <c r="M28" s="126">
+      <c r="M28" s="120">
         <f t="shared" si="19"/>
         <v>0.17992803842801047</v>
       </c>
     </row>
     <row r="29" spans="2:13" ht="16">
-      <c r="B29" s="80" t="s">
+      <c r="B29" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="125">
+      <c r="C29" s="119">
         <f>C18/C8</f>
         <v>0.23072471265000349</v>
       </c>
-      <c r="D29" s="125">
+      <c r="D29" s="119">
         <f t="shared" ref="D29:H29" si="20">D18/D8</f>
         <v>0.28941584905660378</v>
       </c>
-      <c r="E29" s="125">
+      <c r="E29" s="119">
         <f t="shared" si="20"/>
         <v>0.17399870736931003</v>
       </c>
-      <c r="F29" s="125">
+      <c r="F29" s="119">
         <f t="shared" si="20"/>
         <v>0.2744021515045571</v>
       </c>
-      <c r="G29" s="125">
+      <c r="G29" s="119">
         <f t="shared" si="20"/>
         <v>0.14279458200190126</v>
       </c>
-      <c r="H29" s="125">
+      <c r="H29" s="119">
         <f t="shared" si="20"/>
         <v>0.16871904136397903</v>
       </c>
@@ -2451,13 +2449,13 @@
         <f t="shared" si="21"/>
         <v>0.17751904136397906</v>
       </c>
-      <c r="M29" s="126">
+      <c r="M29" s="120">
         <f t="shared" si="21"/>
         <v>0.17971904136397907</v>
       </c>
     </row>
     <row r="30" spans="2:13" ht="16">
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="79" t="s">
         <v>38</v>
       </c>
       <c r="C30" s="39">
@@ -2490,30 +2488,30 @@
       <c r="L30" s="21">
         <v>0.25</v>
       </c>
-      <c r="M30" s="126">
+      <c r="M30" s="120">
         <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="16">
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="79" t="s">
         <v>39</v>
       </c>
       <c r="C31" s="34">
         <v>76065601</v>
       </c>
-      <c r="D31" s="127">
+      <c r="D31" s="121">
         <v>119952578</v>
       </c>
-      <c r="E31" s="127">
+      <c r="E31" s="121">
         <v>243693689</v>
       </c>
-      <c r="F31" s="127">
+      <c r="F31" s="121">
         <v>283201865</v>
       </c>
-      <c r="G31" s="127">
+      <c r="G31" s="121">
         <v>309371619</v>
       </c>
-      <c r="H31" s="127">
+      <c r="H31" s="121">
         <v>321587316</v>
       </c>
       <c r="I31" s="20">
@@ -2528,34 +2526,34 @@
       <c r="L31" s="20">
         <v>379717705.8777625</v>
       </c>
-      <c r="M31" s="116">
+      <c r="M31" s="110">
         <v>393896365.01523811</v>
       </c>
     </row>
     <row r="32" spans="2:13" ht="16">
-      <c r="B32" s="80" t="s">
+      <c r="B32" s="79" t="s">
         <v>40</v>
       </c>
       <c r="C32" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="81">
+      <c r="D32" s="80">
         <f>(D8-C8)/C8</f>
         <v>6.3346320489256244E-2</v>
       </c>
-      <c r="E32" s="81">
+      <c r="E32" s="80">
         <f t="shared" ref="E32:M32" si="22">(E8-D8)/D8</f>
         <v>0.80363083557951487</v>
       </c>
-      <c r="F32" s="81">
+      <c r="F32" s="80">
         <f t="shared" si="22"/>
         <v>0.20507373087983771</v>
       </c>
-      <c r="G32" s="81">
+      <c r="G32" s="80">
         <f t="shared" si="22"/>
         <v>0.14359812707671024</v>
       </c>
-      <c r="H32" s="81">
+      <c r="H32" s="80">
         <f t="shared" si="22"/>
         <v>8.9321285857575844E-2</v>
       </c>
@@ -2571,12 +2569,12 @@
       <c r="L32" s="31">
         <v>3.7339999999999929E-2</v>
       </c>
-      <c r="M32" s="128">
+      <c r="M32" s="122">
         <v>3.7339999999999929E-2</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="16">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="79" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="42" t="s">
@@ -2614,34 +2612,34 @@
       <c r="L33" s="31">
         <v>0.02</v>
       </c>
-      <c r="M33" s="128">
+      <c r="M33" s="122">
         <v>0.02</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="16">
-      <c r="B34" s="80" t="s">
+      <c r="B34" s="79" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="81">
+      <c r="D34" s="80">
         <f>D31/(D8*1000)</f>
         <v>5.1731570026954179E-2</v>
       </c>
-      <c r="E34" s="81">
+      <c r="E34" s="80">
         <f t="shared" ref="E34:H34" si="24">E31/(E8*1000)</f>
         <v>5.8269689484093064E-2</v>
       </c>
-      <c r="F34" s="81">
+      <c r="F34" s="80">
         <f t="shared" si="24"/>
         <v>5.6192830818231281E-2</v>
       </c>
-      <c r="G34" s="81">
+      <c r="G34" s="80">
         <f t="shared" si="24"/>
         <v>5.3677445128689341E-2</v>
       </c>
-      <c r="H34" s="81">
+      <c r="H34" s="80">
         <f t="shared" si="24"/>
         <v>5.1221735309843995E-2</v>
       </c>
@@ -2657,50 +2655,50 @@
       <c r="L34" s="31">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="M34" s="128">
+      <c r="M34" s="122">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="35" spans="2:13" ht="16">
-      <c r="B35" s="83" t="s">
+      <c r="B35" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="129" t="s">
+      <c r="C35" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="130">
+      <c r="D35" s="124">
         <f>(1+D34)*(1+D33)-1</f>
         <v>0.65854093743005726</v>
       </c>
-      <c r="E35" s="130">
+      <c r="E35" s="124">
         <f t="shared" ref="E35:H35" si="25">(1+E34)*(1+E33)-1</f>
         <v>1.1499633345709599</v>
       </c>
-      <c r="F35" s="130">
+      <c r="F35" s="124">
         <f t="shared" si="25"/>
         <v>0.22742521857984022</v>
       </c>
-      <c r="G35" s="130">
+      <c r="G35" s="124">
         <f t="shared" si="25"/>
         <v>0.15104431640394145</v>
       </c>
-      <c r="H35" s="130">
+      <c r="H35" s="124">
         <f t="shared" si="25"/>
         <v>9.2729764520368629E-2</v>
       </c>
-      <c r="I35" s="131">
+      <c r="I35" s="125">
         <v>4.9544000000000032E-2</v>
       </c>
-      <c r="J35" s="131">
+      <c r="J35" s="125">
         <v>4.3441999999999981E-2</v>
       </c>
-      <c r="K35" s="131">
+      <c r="K35" s="125">
         <v>3.937400000000002E-2</v>
       </c>
-      <c r="L35" s="131">
+      <c r="L35" s="125">
         <v>3.7339999999999929E-2</v>
       </c>
-      <c r="M35" s="132">
+      <c r="M35" s="126">
         <v>3.7339999999999929E-2</v>
       </c>
     </row>
@@ -2774,7 +2772,7 @@
     </row>
     <row r="3" spans="1:17" ht="16">
       <c r="A3" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
@@ -2828,30 +2826,28 @@
       <c r="C6" s="22">
         <v>2025</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="52" t="s">
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="52" t="s">
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="N6" s="53"/>
-      <c r="O6" s="53"/>
-      <c r="P6" s="53"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="52"/>
     </row>
     <row r="7" spans="1:17" ht="16">
-      <c r="C7" s="46" t="s">
-        <v>94</v>
-      </c>
+      <c r="C7" s="46"/>
       <c r="D7" s="46" t="s">
         <v>62</v>
       </c>
@@ -2896,84 +2892,84 @@
       <c r="C8" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50" t="s">
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="N8" s="50" t="s">
+      <c r="N8" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="O8" s="50" t="s">
+      <c r="O8" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="P8" s="50" t="s">
+      <c r="P8" s="49" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="C9" s="100" t="s">
+      <c r="C9" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="101">
+      <c r="D9" s="100">
         <v>23.82</v>
       </c>
-      <c r="E9" s="101">
+      <c r="E9" s="100">
         <v>1499074627</v>
       </c>
-      <c r="F9" s="101">
+      <c r="F9" s="100">
         <f t="shared" ref="F9:F14" si="0">D9*E9</f>
         <v>35707957615.139999</v>
       </c>
-      <c r="G9" s="64">
+      <c r="G9" s="63">
         <v>5509027000</v>
       </c>
-      <c r="H9" s="64">
+      <c r="H9" s="63">
         <f>F9+G9</f>
         <v>41216984615.139999</v>
       </c>
-      <c r="I9" s="64">
+      <c r="I9" s="63">
         <v>5357335000</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="63">
         <v>2988135000</v>
       </c>
-      <c r="K9" s="101">
+      <c r="K9" s="100">
         <v>3785032000</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="100">
         <v>2136676000</v>
       </c>
-      <c r="M9" s="102">
+      <c r="M9" s="101">
         <f>H9/(I9)</f>
         <v>7.6935611857649375</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="101">
         <f t="shared" ref="N9:N14" si="1">H9/(J9)</f>
         <v>13.793548355459174</v>
       </c>
-      <c r="O9" s="102">
+      <c r="O9" s="101">
         <f t="shared" ref="O9:O14" si="2">H9/(K9)</f>
         <v>10.889467939806057</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="102">
         <f t="shared" ref="P9:P14" si="3">F9/(L9)</f>
         <v>16.71191964300624</v>
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="C10" s="80" t="s">
+      <c r="C10" s="79" t="s">
         <v>81</v>
       </c>
       <c r="D10" s="47">
@@ -3018,13 +3014,13 @@
         <f t="shared" si="2"/>
         <v>8.610305968561585</v>
       </c>
-      <c r="P10" s="104">
+      <c r="P10" s="103">
         <f t="shared" si="3"/>
         <v>28.90871847905759</v>
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="C11" s="105" t="s">
+      <c r="C11" s="104" t="s">
         <v>80</v>
       </c>
       <c r="D11" s="47">
@@ -3068,7 +3064,7 @@
         <f t="shared" si="2"/>
         <v>11.895093488455835</v>
       </c>
-      <c r="P11" s="104">
+      <c r="P11" s="103">
         <f t="shared" si="3"/>
         <v>23.015677974299077</v>
       </c>
@@ -3077,7 +3073,7 @@
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="C12" s="80" t="s">
+      <c r="C12" s="79" t="s">
         <v>82</v>
       </c>
       <c r="D12" s="47">
@@ -3121,7 +3117,7 @@
         <f t="shared" si="2"/>
         <v>8.0773421075324343</v>
       </c>
-      <c r="P12" s="104">
+      <c r="P12" s="103">
         <f t="shared" si="3"/>
         <v>35.538717242447028</v>
       </c>
@@ -3130,7 +3126,7 @@
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="79" t="s">
         <v>83</v>
       </c>
       <c r="D13" s="47">
@@ -3174,7 +3170,7 @@
         <f t="shared" si="2"/>
         <v>9.3242645199589553</v>
       </c>
-      <c r="P13" s="104">
+      <c r="P13" s="103">
         <f t="shared" si="3"/>
         <v>17.061615132814847</v>
       </c>
@@ -3183,7 +3179,7 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="C14" s="80" t="s">
+      <c r="C14" s="79" t="s">
         <v>84</v>
       </c>
       <c r="D14" s="47">
@@ -3226,7 +3222,7 @@
         <f t="shared" si="2"/>
         <v>6.1213754981747162</v>
       </c>
-      <c r="P14" s="104">
+      <c r="P14" s="103">
         <f t="shared" si="3"/>
         <v>22.821939031162188</v>
       </c>
@@ -3235,115 +3231,115 @@
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="C15" s="106" t="s">
+      <c r="C15" s="152" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="153">
         <f t="shared" ref="D15:L15" si="5">SUM(D9:D14)/6</f>
         <v>237.46333333333334</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="153">
         <f t="shared" si="5"/>
         <v>315357870.83333331</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="153">
         <f t="shared" si="5"/>
         <v>12093165808.051666</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="153">
         <f t="shared" si="5"/>
         <v>3013889405.5</v>
       </c>
-      <c r="H15" s="49">
+      <c r="H15" s="153">
         <f t="shared" si="5"/>
         <v>15006039090.218332</v>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="153">
         <f t="shared" si="5"/>
         <v>3133293790.1333332</v>
       </c>
-      <c r="J15" s="49">
+      <c r="J15" s="153">
         <f t="shared" si="5"/>
         <v>1022502815.3333334</v>
       </c>
-      <c r="K15" s="49">
+      <c r="K15" s="153">
         <f t="shared" si="5"/>
         <v>1548893825.8333333</v>
       </c>
-      <c r="L15" s="49">
+      <c r="L15" s="153">
         <f t="shared" si="5"/>
         <v>608525127.33333337</v>
       </c>
-      <c r="M15" s="49">
+      <c r="M15" s="154">
         <f t="shared" ref="M15:P15" si="6">SUM(M9:M14)/6</f>
         <v>4.6777910282312538</v>
       </c>
-      <c r="N15" s="49">
+      <c r="N15" s="154">
         <f t="shared" si="6"/>
         <v>14.807576801832719</v>
       </c>
-      <c r="O15" s="49">
+      <c r="O15" s="154">
         <f t="shared" si="6"/>
         <v>9.1529749204149322</v>
       </c>
-      <c r="P15" s="107">
+      <c r="P15" s="155">
         <f t="shared" si="6"/>
         <v>24.009764583797828</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="C16" s="108" t="s">
+      <c r="C16" s="156" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="109">
+      <c r="D16" s="157">
         <f t="shared" ref="D16:P16" si="7">MEDIAN(D9:D14)</f>
         <v>90.5</v>
       </c>
-      <c r="E16" s="109">
+      <c r="E16" s="157">
         <f t="shared" si="7"/>
         <v>95738998</v>
       </c>
-      <c r="F16" s="109">
+      <c r="F16" s="157">
         <f t="shared" si="7"/>
         <v>7855973864.2849998</v>
       </c>
-      <c r="G16" s="109">
+      <c r="G16" s="157">
         <f t="shared" si="7"/>
         <v>1214298263.5</v>
       </c>
-      <c r="H16" s="109">
+      <c r="H16" s="157">
         <f t="shared" si="7"/>
         <v>9070272127.7849998</v>
       </c>
-      <c r="I16" s="109">
+      <c r="I16" s="157">
         <f t="shared" si="7"/>
         <v>1829745424</v>
       </c>
-      <c r="J16" s="109">
+      <c r="J16" s="157">
         <f t="shared" si="7"/>
         <v>531424015.5</v>
       </c>
-      <c r="K16" s="109">
+      <c r="K16" s="157">
         <f t="shared" si="7"/>
         <v>879836383</v>
       </c>
-      <c r="L16" s="109">
+      <c r="L16" s="157">
         <f t="shared" si="7"/>
         <v>377293463</v>
       </c>
-      <c r="M16" s="109">
+      <c r="M16" s="158">
         <f t="shared" si="7"/>
         <v>4.2130773422321806</v>
       </c>
-      <c r="N16" s="109">
+      <c r="N16" s="158">
         <f t="shared" si="7"/>
         <v>14.57578921389954</v>
       </c>
-      <c r="O16" s="109">
+      <c r="O16" s="158">
         <f t="shared" si="7"/>
         <v>8.9672852442602711</v>
       </c>
-      <c r="P16" s="110">
+      <c r="P16" s="159">
         <f t="shared" si="7"/>
         <v>22.918808502730634</v>
       </c>
@@ -3386,7 +3382,7 @@
     <mergeCell ref="G6:L6"/>
     <mergeCell ref="M6:P6"/>
   </mergeCells>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3438,7 +3434,7 @@
     </row>
     <row r="3" spans="1:14" ht="16">
       <c r="A3" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -3463,101 +3459,101 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="16">
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="91">
         <v>2.9767999999999999E-2</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16">
-      <c r="C8" s="87" t="s">
+      <c r="C8" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="93">
+      <c r="D8" s="92">
         <v>0.89</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16">
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="94">
+      <c r="D9" s="93">
         <v>5.7799999999999997E-2</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16">
-      <c r="C10" s="87" t="s">
+      <c r="C10" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="95">
+      <c r="D10" s="94">
         <v>8.1210000000000004E-2</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16">
-      <c r="C11" s="87" t="s">
+      <c r="C11" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="94">
+      <c r="D11" s="93">
         <f>124354/7556696</f>
         <v>1.6456133738872121E-2</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16">
-      <c r="C12" s="87" t="s">
+      <c r="C12" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="95">
+      <c r="D12" s="94">
         <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16">
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="96">
+      <c r="D13" s="95">
         <v>0.17466211719202615</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16">
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="97">
+      <c r="D14" s="96">
         <f>1-D13</f>
         <v>0.82533788280797382</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16">
-      <c r="C15" s="87" t="s">
+      <c r="C15" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="97">
+      <c r="D15" s="96">
         <f>D14*D10+D13*D11*(1-D12)</f>
         <v>6.9181386832555467E-2</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16">
-      <c r="C16" s="89" t="s">
+      <c r="C16" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="95">
+      <c r="D16" s="94">
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
     <row r="17" spans="3:5" ht="16">
-      <c r="C17" s="89" t="s">
+      <c r="C17" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="98">
+      <c r="D17" s="97">
         <v>5509027000</v>
       </c>
     </row>
     <row r="18" spans="3:5" ht="16">
-      <c r="C18" s="91" t="s">
+      <c r="C18" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="99">
+      <c r="D18" s="98">
         <v>1499074627</v>
       </c>
     </row>
@@ -3565,7 +3561,7 @@
       <c r="E22" s="7"/>
     </row>
     <row r="23" spans="3:5">
-      <c r="E23" s="66"/>
+      <c r="E23" s="65"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3624,7 +3620,7 @@
     </row>
     <row r="3" spans="1:15" ht="16">
       <c r="A3" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
@@ -3642,35 +3638,35 @@
       <c r="O3" s="26"/>
     </row>
     <row r="7" spans="1:15" ht="16">
-      <c r="E7" s="58" t="s">
+      <c r="E7" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="59"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="58"/>
     </row>
     <row r="8" spans="1:15" ht="16">
       <c r="D8" s="30">
         <v>2025</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="50">
         <v>2026</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="50">
         <v>2027</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="50">
         <v>2028</v>
       </c>
-      <c r="H8" s="51">
+      <c r="H8" s="50">
         <v>2029</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="50">
         <v>2030</v>
       </c>
-      <c r="J8" s="51">
+      <c r="J8" s="50">
         <v>2031</v>
       </c>
     </row>
@@ -3687,255 +3683,255 @@
       <c r="J9" s="22"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="54">
         <v>2067637250</v>
       </c>
-      <c r="E10" s="62">
+      <c r="E10" s="61">
         <v>2186027966.1870499</v>
       </c>
-      <c r="F10" s="62">
+      <c r="F10" s="61">
         <v>2277993945.0883498</v>
       </c>
-      <c r="G10" s="62">
+      <c r="G10" s="61">
         <v>2341669109.9993801</v>
       </c>
-      <c r="H10" s="62">
+      <c r="H10" s="61">
         <v>2490256500.9137001</v>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="61">
         <v>2614164336.8742299</v>
       </c>
-      <c r="J10" s="133">
+      <c r="J10" s="127">
         <f>I10*(1+J13)</f>
         <v>2659912212.7695293</v>
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="C11" s="80"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="138"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="132"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="C12" s="80" t="s">
+      <c r="C12" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="137">
+      <c r="D12" s="131">
         <v>6.9181386832555467E-2</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="64">
         <v>6.9181386832555467E-2</v>
       </c>
-      <c r="F12" s="65">
+      <c r="F12" s="64">
         <v>6.9181386832555467E-2</v>
       </c>
-      <c r="G12" s="65">
+      <c r="G12" s="64">
         <v>6.9181386832555467E-2</v>
       </c>
-      <c r="H12" s="65">
+      <c r="H12" s="64">
         <v>6.9181386832555467E-2</v>
       </c>
-      <c r="I12" s="65">
+      <c r="I12" s="64">
         <v>6.9181386832555467E-2</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="132">
         <v>6.9181386832555467E-2</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="C13" s="80" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="81">
+      <c r="C13" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="80">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="E13" s="135">
+      <c r="E13" s="129">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="F13" s="135">
+      <c r="F13" s="129">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="G13" s="135">
+      <c r="G13" s="129">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="H13" s="135">
+      <c r="H13" s="129">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="I13" s="135">
+      <c r="I13" s="129">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="J13" s="136">
+      <c r="J13" s="130">
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="C14" s="80" t="s">
+      <c r="C14" s="79" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="34">
         <v>1</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="59">
         <f>1/(1+E12)</f>
         <v>0.9352949951387528</v>
       </c>
-      <c r="F14" s="60">
+      <c r="F14" s="59">
         <f xml:space="preserve"> 1 /(1 + $E$12)^2</f>
         <v>0.87477672793159977</v>
       </c>
-      <c r="G14" s="60">
+      <c r="G14" s="59">
         <f xml:space="preserve"> 1 /(1 + $E$12)^3</f>
         <v>0.8181742954982798</v>
       </c>
-      <c r="H14" s="60">
+      <c r="H14" s="59">
         <f xml:space="preserve"> 1 /(1 + $E$12)^4</f>
         <v>0.7652343237307162</v>
       </c>
-      <c r="I14" s="60">
+      <c r="I14" s="59">
         <f xml:space="preserve"> 1 /(1 + $E$12)^5</f>
         <v>0.71571983309372711</v>
       </c>
-      <c r="J14" s="134"/>
+      <c r="J14" s="128"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="C15" s="80"/>
+      <c r="C15" s="79"/>
       <c r="D15" s="34"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="138"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="132"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="C16" s="80" t="s">
+      <c r="C16" s="79" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="34"/>
-      <c r="E16" s="60">
+      <c r="E16" s="59">
         <f>E14*E10</f>
         <v>2044581016.0080945</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="59">
         <f t="shared" ref="F16:I16" si="0">F14*F10</f>
         <v>1992736089.532383</v>
       </c>
-      <c r="G16" s="60">
+      <c r="G16" s="59">
         <f>G14*G10</f>
         <v>1915893474.3638268</v>
       </c>
-      <c r="H16" s="60">
+      <c r="H16" s="59">
         <f t="shared" si="0"/>
         <v>1905629749.392715</v>
       </c>
-      <c r="I16" s="60">
+      <c r="I16" s="59">
         <f t="shared" si="0"/>
         <v>1871009262.8671978</v>
       </c>
-      <c r="J16" s="138"/>
+      <c r="J16" s="132"/>
     </row>
     <row r="17" spans="3:10" ht="16">
-      <c r="C17" s="80"/>
+      <c r="C17" s="79"/>
       <c r="D17" s="34"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="138"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="141"/>
+      <c r="J17" s="132"/>
     </row>
     <row r="18" spans="3:10">
-      <c r="C18" s="148" t="s">
+      <c r="C18" s="142" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="34"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60">
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59">
         <f>J10*(1+I13)/(I12-I13)</f>
         <v>52368189833.252029</v>
       </c>
-      <c r="J18" s="138"/>
+      <c r="J18" s="132"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="80" t="s">
+      <c r="C19" s="79" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="34"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="134"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="128"/>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="80" t="s">
+      <c r="C20" s="79" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="34">
         <f>SUM(E16:I16)+(I18/(1+D12)^5)</f>
         <v>47210801679.03997</v>
       </c>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="134"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="59"/>
+      <c r="J20" s="128"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="80" t="s">
-        <v>104</v>
+      <c r="C21" s="79" t="s">
+        <v>103</v>
       </c>
       <c r="D21" s="34">
         <v>5509027000</v>
       </c>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="134"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="128"/>
     </row>
     <row r="22" spans="3:10">
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="79" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="34">
         <f>D20-D21</f>
         <v>41701774679.03997</v>
       </c>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="134"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="128"/>
     </row>
     <row r="23" spans="3:10">
-      <c r="C23" s="151" t="s">
+      <c r="C23" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="152">
+      <c r="D23" s="146">
         <f>D22/1499074627</f>
         <v>27.818344682742715</v>
       </c>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="150"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="144"/>
     </row>
     <row r="28" spans="3:10" ht="16">
       <c r="E28" s="32" t="s">
@@ -3979,438 +3975,438 @@
       <c r="I30" s="24"/>
     </row>
     <row r="31" spans="3:10">
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="55">
+      <c r="D31" s="54">
         <v>2241101.25</v>
       </c>
-      <c r="E31" s="62">
+      <c r="E31" s="61">
         <v>2337433.78706775</v>
       </c>
-      <c r="F31" s="62">
+      <c r="F31" s="61">
         <v>2425027.4127782797</v>
       </c>
-      <c r="G31" s="62">
+      <c r="G31" s="61">
         <v>2502540.8391279019</v>
       </c>
-      <c r="H31" s="62">
+      <c r="H31" s="61">
         <v>2568741.7159578735</v>
       </c>
-      <c r="I31" s="133">
+      <c r="I31" s="127">
         <v>2622538.4839680172</v>
       </c>
     </row>
     <row r="32" spans="3:10">
-      <c r="C32" s="80" t="s">
+      <c r="C32" s="79" t="s">
         <v>32</v>
       </c>
       <c r="D32" s="34">
         <v>-88914</v>
       </c>
-      <c r="E32" s="60">
+      <c r="E32" s="59">
         <v>-114454.91232</v>
       </c>
-      <c r="F32" s="60">
+      <c r="F32" s="59">
         <v>-141582.10518648001</v>
       </c>
-      <c r="G32" s="60">
+      <c r="G32" s="59">
         <v>-169997.0805784541</v>
       </c>
-      <c r="H32" s="60">
+      <c r="H32" s="59">
         <v>-199352.18072273867</v>
       </c>
-      <c r="I32" s="134">
+      <c r="I32" s="128">
         <v>-229256.72527033903</v>
       </c>
     </row>
     <row r="33" spans="3:9">
-      <c r="C33" s="80" t="s">
+      <c r="C33" s="79" t="s">
         <v>30</v>
       </c>
       <c r="D33" s="34">
         <v>1059275</v>
       </c>
-      <c r="E33" s="60">
+      <c r="E33" s="59">
         <v>1126741.7084700002</v>
       </c>
-      <c r="F33" s="60">
+      <c r="F33" s="59">
         <v>1192030.0546188301</v>
       </c>
-      <c r="G33" s="60">
+      <c r="G33" s="59">
         <v>1254258.3521356343</v>
       </c>
-      <c r="H33" s="60">
+      <c r="H33" s="59">
         <v>1312542.3930193011</v>
       </c>
-      <c r="I33" s="134">
+      <c r="I33" s="128">
         <v>1366015.4249214039</v>
       </c>
     </row>
     <row r="34" spans="3:9">
-      <c r="C34" s="80" t="s">
+      <c r="C34" s="79" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="34">
         <v>796897</v>
       </c>
-      <c r="E34" s="60">
+      <c r="E34" s="59">
         <v>906619.7408100001</v>
       </c>
-      <c r="F34" s="60">
+      <c r="F34" s="59">
         <v>1019951.7762270902</v>
       </c>
-      <c r="G34" s="60">
+      <c r="G34" s="59">
         <v>1135563.8632720823</v>
       </c>
-      <c r="H34" s="60">
+      <c r="H34" s="59">
         <v>1251979.6583841993</v>
       </c>
-      <c r="I34" s="134">
+      <c r="I34" s="128">
         <v>1367603.9778708487</v>
       </c>
     </row>
     <row r="35" spans="3:9">
-      <c r="C35" s="80" t="s">
+      <c r="C35" s="79" t="s">
         <v>57</v>
       </c>
       <c r="D35" s="34">
         <v>12094818</v>
       </c>
-      <c r="E35" s="60">
+      <c r="E35" s="59">
         <f>D35+E33-E34</f>
         <v>12314939.967660001</v>
       </c>
-      <c r="F35" s="60">
+      <c r="F35" s="59">
         <f t="shared" ref="F35:I35" si="1">E35+F33-F34</f>
         <v>12487018.24605174</v>
       </c>
-      <c r="G35" s="60">
+      <c r="G35" s="59">
         <f t="shared" si="1"/>
         <v>12605712.734915292</v>
       </c>
-      <c r="H35" s="60">
+      <c r="H35" s="59">
         <f t="shared" si="1"/>
         <v>12666275.469550394</v>
       </c>
-      <c r="I35" s="134">
+      <c r="I35" s="128">
         <f t="shared" si="1"/>
         <v>12664686.91660095</v>
       </c>
     </row>
     <row r="36" spans="3:9">
-      <c r="C36" s="80" t="s">
+      <c r="C36" s="79" t="s">
         <v>50</v>
       </c>
       <c r="D36" s="34">
         <f>D35+D32</f>
         <v>12005904</v>
       </c>
-      <c r="E36" s="60">
+      <c r="E36" s="59">
         <f t="shared" ref="E36:I36" si="2">E35+E32</f>
         <v>12200485.055340001</v>
       </c>
-      <c r="F36" s="60">
+      <c r="F36" s="59">
         <f t="shared" si="2"/>
         <v>12345436.140865261</v>
       </c>
-      <c r="G36" s="60">
+      <c r="G36" s="59">
         <f t="shared" si="2"/>
         <v>12435715.654336838</v>
       </c>
-      <c r="H36" s="60">
+      <c r="H36" s="59">
         <f t="shared" si="2"/>
         <v>12466923.288827654</v>
       </c>
-      <c r="I36" s="134">
+      <c r="I36" s="128">
         <f t="shared" si="2"/>
         <v>12435430.191330612</v>
       </c>
     </row>
     <row r="37" spans="3:9">
-      <c r="C37" s="80" t="s">
+      <c r="C37" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="81">
+      <c r="D37" s="80">
         <f>D31/((D36+11728774)/2)</f>
         <v>0.1888461473966489</v>
       </c>
-      <c r="E37" s="135">
+      <c r="E37" s="129">
         <f>E31/((E36+D36)/2)</f>
         <v>0.19312535890619384</v>
       </c>
-      <c r="F37" s="135">
+      <c r="F37" s="129">
         <f t="shared" ref="F37:I37" si="3">F31/((F36+E36)/2)</f>
         <v>0.19759106968478191</v>
       </c>
-      <c r="G37" s="135">
+      <c r="G37" s="129">
         <f t="shared" si="3"/>
         <v>0.2019713094701612</v>
       </c>
-      <c r="H37" s="135">
+      <c r="H37" s="129">
         <f t="shared" si="3"/>
         <v>0.20630277151112661</v>
       </c>
-      <c r="I37" s="136">
+      <c r="I37" s="130">
         <f t="shared" si="3"/>
         <v>0.21062575359052768</v>
       </c>
     </row>
     <row r="38" spans="3:9">
-      <c r="C38" s="80" t="s">
+      <c r="C38" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="137">
+      <c r="D38" s="131">
         <v>6.9181386832555467E-2</v>
       </c>
-      <c r="E38" s="65">
+      <c r="E38" s="64">
         <v>6.9181000000000006E-2</v>
       </c>
-      <c r="F38" s="65">
+      <c r="F38" s="64">
         <v>6.9181000000000006E-2</v>
       </c>
-      <c r="G38" s="65">
+      <c r="G38" s="64">
         <v>6.9181000000000006E-2</v>
       </c>
-      <c r="H38" s="65">
+      <c r="H38" s="64">
         <v>6.9181000000000006E-2</v>
       </c>
-      <c r="I38" s="138">
+      <c r="I38" s="132">
         <v>6.9181000000000006E-2</v>
       </c>
     </row>
     <row r="39" spans="3:9">
-      <c r="C39" s="80" t="s">
+      <c r="C39" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="137">
+      <c r="D39" s="131">
         <f>D37-D38</f>
         <v>0.11966476056409343</v>
       </c>
-      <c r="E39" s="65">
+      <c r="E39" s="64">
         <f t="shared" ref="E39:I39" si="4">E37-E38</f>
         <v>0.12394435890619383</v>
       </c>
-      <c r="F39" s="65">
+      <c r="F39" s="64">
         <f t="shared" si="4"/>
         <v>0.12841006968478191</v>
       </c>
-      <c r="G39" s="65">
+      <c r="G39" s="64">
         <f t="shared" si="4"/>
         <v>0.13279030947016118</v>
       </c>
-      <c r="H39" s="65">
+      <c r="H39" s="64">
         <f t="shared" si="4"/>
         <v>0.13712177151112659</v>
       </c>
-      <c r="I39" s="138">
+      <c r="I39" s="132">
         <f t="shared" si="4"/>
         <v>0.14144475359052766</v>
       </c>
     </row>
     <row r="40" spans="3:9">
-      <c r="C40" s="80"/>
+      <c r="C40" s="79"/>
       <c r="D40" s="33"/>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="140"/>
+      <c r="E40" s="133"/>
+      <c r="F40" s="133"/>
+      <c r="G40" s="133"/>
+      <c r="H40" s="133"/>
+      <c r="I40" s="134"/>
     </row>
     <row r="41" spans="3:9">
-      <c r="C41" s="80" t="s">
+      <c r="C41" s="79" t="s">
         <v>53</v>
       </c>
       <c r="D41" s="34">
         <f>D33-D34+D32</f>
         <v>173464</v>
       </c>
-      <c r="E41" s="60">
+      <c r="E41" s="59">
         <f t="shared" ref="E41:I41" si="5">E33-E34+E32</f>
         <v>105667.05534000008</v>
       </c>
-      <c r="F41" s="60">
+      <c r="F41" s="59">
         <f t="shared" si="5"/>
         <v>30496.173205259925</v>
       </c>
-      <c r="G41" s="60">
+      <c r="G41" s="59">
         <f t="shared" si="5"/>
         <v>-51302.591714902112</v>
       </c>
-      <c r="H41" s="60">
+      <c r="H41" s="59">
         <f t="shared" si="5"/>
         <v>-138789.44608763681</v>
       </c>
-      <c r="I41" s="134">
+      <c r="I41" s="128">
         <f t="shared" si="5"/>
         <v>-230845.27821978388</v>
       </c>
     </row>
     <row r="42" spans="3:9">
-      <c r="C42" s="80" t="s">
+      <c r="C42" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="D42" s="81">
+      <c r="D42" s="80">
         <f>D41/D31</f>
         <v>7.7401232987576979E-2</v>
       </c>
-      <c r="E42" s="135">
+      <c r="E42" s="129">
         <f t="shared" ref="E42:I42" si="6">E41/E31</f>
         <v>4.5206437899811769E-2</v>
       </c>
-      <c r="F42" s="135">
+      <c r="F42" s="129">
         <f t="shared" si="6"/>
         <v>1.2575599370368104E-2</v>
       </c>
-      <c r="G42" s="135">
+      <c r="G42" s="129">
         <f t="shared" si="6"/>
         <v>-2.0500201600218558E-2</v>
       </c>
-      <c r="H42" s="135">
+      <c r="H42" s="129">
         <f t="shared" si="6"/>
         <v>-5.4030128924769216E-2</v>
       </c>
-      <c r="I42" s="136">
+      <c r="I42" s="130">
         <f t="shared" si="6"/>
         <v>-8.8023599894139493E-2</v>
       </c>
     </row>
     <row r="43" spans="3:9">
-      <c r="C43" s="80" t="s">
+      <c r="C43" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="141">
+      <c r="D43" s="135">
         <f>D42*D37</f>
         <v>1.4616924653454325E-2</v>
       </c>
-      <c r="E43" s="142">
+      <c r="E43" s="136">
         <f t="shared" ref="E43:I43" si="7">E42*E37</f>
         <v>8.7305095442717119E-3</v>
       </c>
-      <c r="F43" s="142">
+      <c r="F43" s="136">
         <f t="shared" si="7"/>
         <v>2.4848261315183035E-3</v>
       </c>
-      <c r="G43" s="142">
+      <c r="G43" s="136">
         <f t="shared" si="7"/>
         <v>-4.1404525615984364E-3</v>
       </c>
-      <c r="H43" s="142">
+      <c r="H43" s="136">
         <f t="shared" si="7"/>
         <v>-1.1146565342283376E-2</v>
       </c>
-      <c r="I43" s="143">
+      <c r="I43" s="137">
         <f t="shared" si="7"/>
         <v>-1.8540037061454222E-2</v>
       </c>
     </row>
     <row r="44" spans="3:9">
-      <c r="C44" s="80" t="s">
+      <c r="C44" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="81">
+      <c r="D44" s="80">
         <f>D37-D42</f>
         <v>0.11144491440907192</v>
       </c>
-      <c r="E44" s="135">
+      <c r="E44" s="129">
         <f t="shared" ref="E44:I44" si="8">E37-E42</f>
         <v>0.14791892100638207</v>
       </c>
-      <c r="F44" s="135">
+      <c r="F44" s="129">
         <f t="shared" si="8"/>
         <v>0.18501547031441379</v>
       </c>
-      <c r="G44" s="135">
+      <c r="G44" s="129">
         <f t="shared" si="8"/>
         <v>0.22247151107037977</v>
       </c>
-      <c r="H44" s="135">
+      <c r="H44" s="129">
         <f t="shared" si="8"/>
         <v>0.26033290043589585</v>
       </c>
-      <c r="I44" s="136">
+      <c r="I44" s="130">
         <f t="shared" si="8"/>
         <v>0.29864935348466715</v>
       </c>
     </row>
     <row r="45" spans="3:9">
-      <c r="C45" s="83" t="s">
+      <c r="C45" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="D45" s="130">
+      <c r="D45" s="124">
         <v>8.9321285857575844E-2</v>
       </c>
-      <c r="E45" s="144">
+      <c r="E45" s="138">
         <v>5.0000000000000086E-2</v>
       </c>
-      <c r="F45" s="144">
+      <c r="F45" s="138">
         <v>4.4499999999999998E-2</v>
       </c>
-      <c r="G45" s="144">
+      <c r="G45" s="138">
         <v>3.8999999999999937E-2</v>
       </c>
-      <c r="H45" s="145">
+      <c r="H45" s="139">
         <v>3.3499999999999912E-2</v>
       </c>
-      <c r="I45" s="146">
+      <c r="I45" s="140">
         <v>2.7999999999999747E-2</v>
       </c>
     </row>
     <row r="51" spans="3:4" ht="16">
       <c r="C51" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="22"/>
+    </row>
+    <row r="52" spans="3:4">
+      <c r="C52" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="147">
+        <v>47210801679.03997</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4">
+      <c r="C53" s="148" t="s">
         <v>108</v>
       </c>
-      <c r="D51" s="22"/>
-    </row>
-    <row r="52" spans="3:4">
-      <c r="C52" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="153">
-        <v>47210801679.03997</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4">
-      <c r="C53" s="154" t="s">
-        <v>109</v>
-      </c>
-      <c r="D53" s="90">
+      <c r="D53" s="89">
         <v>5509027000</v>
       </c>
     </row>
     <row r="54" spans="3:4">
-      <c r="C54" s="155" t="s">
+      <c r="C54" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="156">
+      <c r="D54" s="150">
         <v>41701774679.03997</v>
       </c>
     </row>
     <row r="55" spans="3:4">
-      <c r="C55" s="80"/>
-      <c r="D55" s="88"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="87"/>
     </row>
     <row r="56" spans="3:4">
-      <c r="C56" s="80" t="s">
+      <c r="C56" s="79" t="s">
+        <v>104</v>
+      </c>
+      <c r="D56" s="72">
+        <v>27.818344682742715</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4">
+      <c r="C57" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="D56" s="73">
-        <v>27.818344682742715</v>
-      </c>
-    </row>
-    <row r="57" spans="3:4">
-      <c r="C57" s="80" t="s">
+      <c r="D57" s="87">
+        <v>23.82</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4">
+      <c r="C58" s="143" t="s">
         <v>106</v>
       </c>
-      <c r="D57" s="88">
-        <v>23.82</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4">
-      <c r="C58" s="149" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" s="157">
+      <c r="D58" s="151">
         <f>(D56-D57)/D57</f>
         <v>0.16785661976249852</v>
       </c>
@@ -4482,7 +4478,7 @@
     </row>
     <row r="3" spans="1:16" ht="16">
       <c r="A3" s="27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
@@ -4504,49 +4500,49 @@
       <c r="C6" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="C7" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" s="69">
+      <c r="C7" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="68">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E7" s="69">
+      <c r="E7" s="68">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="F7" s="70">
+      <c r="F7" s="69">
         <v>0.02</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="C8" s="71">
+      <c r="C8" s="70">
         <v>0.06</v>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="71">
         <v>32.375993535879758</v>
       </c>
-      <c r="E8" s="72">
+      <c r="E8" s="71">
         <v>34.181606797934826</v>
       </c>
-      <c r="F8" s="73">
+      <c r="F8" s="72">
         <v>36.212921717746759</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="C9" s="71">
+      <c r="C9" s="70">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="D9" s="72">
+      <c r="D9" s="71">
         <v>28.729246514079716</v>
       </c>
-      <c r="E9" s="72">
+      <c r="E9" s="71">
         <v>30.156126990767497</v>
       </c>
-      <c r="F9" s="73">
+      <c r="F9" s="72">
         <v>31.741549742642782</v>
       </c>
       <c r="I9" s="7"/>
@@ -4556,44 +4552,44 @@
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="C10" s="71">
+      <c r="C10" s="70">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="71">
         <v>25.746276941209018</v>
       </c>
-      <c r="E10" s="72">
+      <c r="E10" s="71">
         <v>26.898117951585125</v>
       </c>
-      <c r="F10" s="73">
+      <c r="F10" s="72">
         <v>28.165143062998823</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="C11" s="71">
+      <c r="C11" s="70">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="D11" s="72">
+      <c r="D11" s="71">
         <v>23.261123832006099</v>
       </c>
-      <c r="E11" s="72">
+      <c r="E11" s="71">
         <v>24.207353778848368</v>
       </c>
-      <c r="F11" s="73">
+      <c r="F11" s="72">
         <v>25.239604629949007</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="C12" s="71">
+      <c r="C12" s="70">
         <v>0.08</v>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="71">
         <v>21.158891576064281</v>
       </c>
-      <c r="E12" s="72">
+      <c r="E12" s="71">
         <v>21.94768130134814</v>
       </c>
-      <c r="F12" s="73">
+      <c r="F12" s="72">
         <v>22.80220350373898</v>
       </c>
       <c r="I12" s="7"/>
@@ -4603,16 +4599,16 @@
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="C13" s="74">
+      <c r="C13" s="73">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="74">
         <v>19.357512289333087</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="74">
         <v>20.023289423218831</v>
       </c>
-      <c r="F13" s="76">
+      <c r="F13" s="75">
         <v>20.74028018278808</v>
       </c>
       <c r="I13" s="9"/>
@@ -4643,17 +4639,17 @@
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="3:13" ht="16">
-      <c r="C17" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="67" t="s">
+      <c r="C17" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="67" t="s">
+      <c r="F17" s="66" t="s">
         <v>96</v>
-      </c>
-      <c r="F17" s="67" t="s">
-        <v>97</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -4662,17 +4658,17 @@
       <c r="M17" s="9"/>
     </row>
     <row r="18" spans="3:13">
-      <c r="C18" s="68" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="77">
+      <c r="C18" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="76">
         <v>2.3E-2</v>
       </c>
-      <c r="E18" s="78">
+      <c r="E18" s="77">
         <f>POWER(('Operating Forecast'!M8/'Operating Forecast'!H8),1/5)-1</f>
         <v>3.897088448772501E-2</v>
       </c>
-      <c r="F18" s="79">
+      <c r="F18" s="78">
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="I18" s="7"/>
@@ -4682,17 +4678,17 @@
       <c r="M18" s="9"/>
     </row>
     <row r="19" spans="3:13">
-      <c r="C19" s="80" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="81">
+      <c r="C19" s="79" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="80">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="E19" s="39">
         <f>POWER(('Operating Forecast'!M10/'Operating Forecast'!H10),1/5)-1</f>
         <v>5.1454662843050336E-2</v>
       </c>
-      <c r="F19" s="82">
+      <c r="F19" s="81">
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="I19" s="7"/>
@@ -4702,17 +4698,17 @@
       <c r="M19" s="9"/>
     </row>
     <row r="20" spans="3:13">
-      <c r="C20" s="83" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" s="84">
+      <c r="C20" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="83">
         <f>E20-1</f>
         <v>9.8894679398060568</v>
       </c>
-      <c r="E20" s="84">
+      <c r="E20" s="83">
         <v>10.889467939806057</v>
       </c>
-      <c r="F20" s="85">
+      <c r="F20" s="84">
         <f>E20+1</f>
         <v>11.889467939806057</v>
       </c>
